--- a/04_extract_results/ai_review_batches/batch_003.xlsx
+++ b/04_extract_results/ai_review_batches/batch_003.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H151"/>
+  <dimension ref="A1:N151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,25 +446,55 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>previous_sentence</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>sentence</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>next_sentence</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ai_relevant</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>relevance_level</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>sentence_type</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>rule_matched_pathways</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>matched_keywords</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>ethanol_specific</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>oxygenate_related</t>
         </is>
@@ -486,27 +516,55 @@
           <t>S0301</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>When applying a bias of –1.3V, the formation of structure (R-Hex-2Cu-O/G), which was used for all reaction *HOCCOHbecomesthermodynamicallydownhill(ΔE=–0.87eV)with mechanismstudy. aloweractivationenergybarrierof0.72eV,leadingtoanacceptable WefirstscrutinizedthekeyreactionintermediatesforC–Ccoureactionrateatroomtemperature46.Ourcalculationalsoconfirms*CO plingonR-Hex-2Cu-O/G,includingtwoCu-adsorbed*CObeforecoutrimerization to form n-propanol is facilitated by the spatialplingandthe*OCCOHdirectlyaftercoupling.Formostoftheactive confinementeffectonR-Hex-2Cu-O/G(SupplementaryFig.36b).The sitesexplored,alinearrelationshipexistsbetweenthetwoadsorption C pathwaytowardn-propanolisshowninFig.5candSupplementary 3 strengths(i.e.,ΔG andΔG )asshowninFig.5aandSuppleFig.40;theU is–0.98V,similartothatforethanolproduction, 2*CO *OCCOH limiting mentary Fig. 35.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>However, some reaction sites significantly deviate and therefore agrees well with the experimental observation for a fromthislinearrelationship,withΔG decreasesfromthetrendnotableselectivitytowardn-propanol(Fig.2a).Nonetheless,itisworth *OCCOH fittedlevelsof1.27,1.21eVto0.92,0.90eV,respectively.ThesereactonotethatgiventhecomplexphasespacedemonstratedbyR-Hextionsitesarethosewithintheconfined-spacebetweentheCu cluster 2Cu-2O/Gthatwouldrequireas-of-yetunrealizedsimulationcapability 9 and the adjacent single Cu center (Supplementary Fig. 35), with an toconclusivelydepict,themechanismproposedhereispendingfor extrabondformedbetweentheadsorbed*OCCOHandadjacentCu furtherclarificationtounderstandthecausalfactorsfromelectronic center (Supplementary Fig. 36a).</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>The extra O–Cu bond boosts the structureandultimatelythecontributionsofstructuralevolutionto *OCCOH adsorption while not affecting the 2*CO adsorption, and theobservedkinetics. thereforebreakthescalingrelationbetweenthesetwocarbonaceous Inshort,ourcalculationsshowthehighlyunder-coordinatedCu intermediatestopromoteC–Ccoupling. clusterinthehybridinorganic/organicstructuresuppressesHERby Additionally,thehighlyunder-coordinatedCuclusteronR-Hexenhancing *CO adsorption, and thereby promotes C–C coupling to 2Cu-O/Gcaninhibitcompetitivehydrogenevolutionreaction(HER), form *OCCOH, which is the PDS.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>P1:*OCCO; P1:OCCO</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>uncertain</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -528,27 +586,55 @@
           <t>S0302</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Furthermore, the confined space further contributing to its higher C selectivity.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>This is achieved betweentheCuclusterandadjacentsingleCucenteraffordsanextra 2 through the significantly enhanced *CO adsorption on the underO–Cu bond to stabilize the *OCCOH intermediate by breaking the coordinated sites.</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>We adopted the selectivity determining method linearscalingrelationwith*CO.Next,CO RRproceedspreferentially 2 proposedbyRossmeisletal45todecidetheproductselectivityonRtowardC HOHformationthroughtheexergonicprotonationonCto 2 5 Hex-2Cu-O/G.TheresultsinFig.5bshowthatallactivesitesfromtheRfrom*OCHCOH,whereastheprotonationonOtoform*HOCCOHis Hex-2Cu-O/G surface (Supplementary Fig. 37) fell in the CO RR disfavoredowingtotheextraenergyneededtocleavetheO–Cubond. 2 dominantzone.Thecalculatedselectivityonthetwomodelsisingood Lastly,theelectrochemicalCO RRofHex-2Cu-Owasfurthertestedina 2 agreementwiththeexperimentalobservationofstableC andalcohol flow-cell using the aqueous 1M KOH electrolyte.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>P1;P3</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>P1:*OCCO; P1:OCCO; P3:COH intermediate</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>uncertain</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -570,19 +656,47 @@
           <t>S0303</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Wefocus on duce high-value multicarbon (C 2+) species at a significant rate3.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>COR and select the Cu(100) as the model surface for a detailed AmongpossibleC products,C oxygenates(Oxys)suchasethanol investigation of the reaction mechanism.</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Computational details 2 2 and acetic acid are produced in liquid forms and possess high and simplifications of the electrochemical models are shown in volumetric energy density and are compatible with existing infraSupplementary Notes 1–5 with corresponding data and justifistructure for easy storage and transportation1,3.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -604,19 +718,47 @@
           <t>S0304</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Owing acetate.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>This feature originates from the competition to the highly reactive nature of cumulative double bonds, ethebetweenmultiplereactionpathways(e.g.,thethreeparallel none issusceptible to nucleophilic attack from water to generate pathways (CHCOH, OCHCH, and CH CO) for CHCO*, aceticacid,i.e.,acetateatneutralandalkalineconditions(Fig.2e). 2 theethenonehydrationvs.CH COreductionforCH CO*) The hydration barrier was experimentally measured to be 2 2 ~0.6eV38,whichisinaccordancewithsimulationsperformedby andthefactthatthesecompetingpathwayspossessdistinct Lucetal.8.Thus,theCH COpathwaynaturallycontributestothe potential dependencies.</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>We will discuss the potential and 2 pH dependencies in more details later. acetate generation.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -638,19 +780,47 @@
           <t>S0305</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>ARTICLE NATURECOMMUNICATIONS|https://doi.org/10.1038/s41467-022-29140-8 The OCHCH pathway.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>Because OCHCH* is thermodynamically Figure3ashowsthetrendsintheoreticalCORcurrentdensities more stable than CHCOH* and CH CO*, it is typically conon Cu(100) obtained through microkinetic modeling, which are 2 sidered an inevitable intermediate in several proposed reaction directly comparable with the experimentally measured CO R (2) mechanisms of ethylene formation26,27.</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>As proposed by Callecurrent densities on planar polycrystalline Cu (pcCu) shown in Vallejo et al.26, one of the reaction steps involves protonation of Fig. 3b.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -672,19 +842,47 @@
           <t>S0306</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>RDS, the Tafel slope of each product consists of two individual From this we conclude, that the production of major C Oxy/ 2 components:onefromthetotalC formationandtheotherfrom HC species under CO R conditions stems from a common 2 (2) relative rates between different pathways.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>Due to the dynamic intermediateofCHCO*.TheprotonationstepsofCHCO*playa nature of the second component, one should be cautious with vitalroleindeterminingtheC productselectivity.TheCHCOH 2 corresponding Tafel analysis. pathway exclusively results in C HC, whereas the OCHCH and 2 Besidesthevariationofreactionrateswithpotential,pHisseen CH CO pathways lead to C Oxy only. 2 2 tohaveaprofoundeffectontheC Oxy/HCselectivity(Fig.3c). 2 To prevent the interference from the different PET number per Microkinetic model of COR and pH effects on C Oxy/HC 2 product molecule, we employed C 2 Oxy/HC molecular ratios selectivity.</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>To further illustrate the important role of CHCO rather than FEs for the selectivity analysis.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -706,19 +904,47 @@
           <t>S0307</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" t="n">
+        <v>26</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>The Cu K-edge XANES suggests a slight electron density decrease in the Cu phase upon Ag introduction, compared to pure Cu.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>DFT calculations demonstrated both the electronic interaction and strain effect of Cu upon Ag incorporation, which shifted the Cu d-band center to a deeper level and thus weakened intermediate adsorption.</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>The oxophilicity of Cu was also reduced as a consequence of compressive strain.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -740,19 +966,43 @@
           <t>S0308</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" t="n">
+        <v>60</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Figure S19 DFT calculated binding energies of *CO and *OH on the (100) and (211) facets of Cu at varying amounts of strain on the crystal.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>Figure S20 DFT calculated scaling line of *OCH CH with *OH, justifying the use of the latter as a descriptor for the binding 2 3 of oxygenate intermediates. 19</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>uncertain</t>
-        </is>
-      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -774,19 +1024,47 @@
           <t>S0309</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Therefore, the feasible strategies are demanded to Mott–Schottky catalyst.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>Thus, the mechanism exploration of lowdevelop the architectural blueprint ofcatalysts and electrolytic syscoordinatedCu/Cu Oonstabilizing*COandoxyhydrocarbonsinter2 temsforpreservingtheoxidationstateandbolsteringtheCO permediatesissignificant. 2 formance of copper-based catalysts, including but not limited to Herein, we demonstrated a low-coordinated Cu/Cu O 2 elemental doping6, interface engineering7,8, intermediate Mott–Schottky catalyst with an enhanced rectifying interface (Cu / L confinement9, and pulse CO electrolysis (P-eCO R owing the Cu O).Thiscatalystadjuststheelectrondensitiesthroughinterfacial 2 2 2 straightforwardandreadilyadjustablemeansofmanipulatinganodic charge exchange, leveraging the difference in Cu and Cu O work 2 potentialsforfacilitatingtheformationofCuoxidespecies)10,11.Espefunctions,whichcaneffectivelyformbondsbetween*COandoxyhycially,theMott−Schottkycatalystpossessestheremarkableabilityto drocarbons under CER conditions.</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Furthermore, Cu /Cu O catalyst L 2 hinder the accumulation of electrons, thereby safeguarding the generatedhighlyselectivecatalyticsitesforthecouplingreactionof integrityofCu–Obonds,whilesimultaneouslyenablingswiftelectron *CO–COHandhydrogenationofC H O*intermediatetoC alcohols. 2 2 2+ transfercourtesyofitsbuilt-inelectricfield12,13.Therefore,itnecessiChlorine-dopedcuprousoxide(Cl–Cu O)andpureCu Owereselec2 2 tatestheemploymentofintricatecatalystconfigurationandfabricated as the precursors and electrochemically reconstructed to tiontechniquestoelevatetherectifyinginterfaceeffectsofCu/Cu O unsaturated-coordinate Cu /Cu O and pure Cu /Cu O.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -808,19 +1086,43 @@
           <t>S0310</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
         <is>
           <t>ARTICLE OPEN https://doi.org/10.1038/s41467-021-20961-7 Morphology and mechanism of highly selective Cu(II) oxide nanosheet catalysts for carbon dioxide electroreduction Xingli Wang 1, Katharina Klingan 2, Malte Klingenhof1, Tim Möller 1, Jorge Ferreira de Araújo1, ✉ Isaac Martens3, Alexander Bagger 4, Shan Jiang2, Jan Rossmeisl 4, Holger Dau 2 &amp; Peter Strasser 1 Cu oxides catalyze the electrochemical carbon dioxide reduction reaction (CO2RR) to hydrocarbons and oxygenates with favorable selectivity.</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Among them, the shape-controlled Cuoxidecubeshavebeenmostwidelystudied.Incontrast,wereportonnovel2-dimensional (2D) Cu(II) oxide nanosheet (CuO NS) catalysts with high C products, selectivities 2+ (&gt; 400mAcm−2) in gas diffusion electrodes (GDE) at industrially relevant currents and neutral pH.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -842,19 +1144,47 @@
           <t>S0311</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Moreover, it exhibited superb longreferencesofCuO,Cu OandCufoil.Theabsorptionedgeofthe 3 2 termCO electroreductiondurabilityover10h.Thewell-defined Cu/N C was between the Cu O and CuO, indicating that the 2 0.14 2 self-reconstructionfortheactivesitesofCu/N Calsofacilitate oxidationstateofthecopperspeciesisintheintermediatevalence 0.14 the in-depth mechanistic understandings from complementary statebetween+1and+2.ThefeatureofXANESat8986eVand Operando Spectroscopy (XAS, XPS and FTIR), XANES simula8997eVforCu/N CresembledthemixturedominatedbyCuO 0.14 tionsandtheoreticalcalculationstopresenttheatomicstructurewith a little contribution by Cu + or Cu0 complex.</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>The Fourieractivity relationship between the ethanol selectivity and in situ transformed (FT) k3-weighted EXAFS oscillation in Fig. 1f also dynamic structure (local structure, electronic structure and the showedthedisappearanceofthefeatureforCu–CuinRspacein adsorbed intermediates), that would benefit the recognition for Cu/N Cwithsimultaneousappearanceofthepeakat1.5Åfor 0.14 the CO RR process.</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Cu−O/N.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -876,19 +1206,47 @@
           <t>S0312</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" t="n">
+        <v>9</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>The N-doping played an important role to dischemicalworkstation(ShanghaiChenhua,China)wasusedtoapplyvoltagetoa perse the reduced Cu n cluster uniformly and adjust charge disself-madeinfraredreflectioncell.Theinfraredspectrumswerecollectedusing tributionbetweenmetalatomsandsubstrate.OperandoFTIRand BrukerVertex70V/sFTIRspectrometerwithnitrogencooledmercurycadmium theoretic calculations results demonstrated that CH * was the telluridedetector,andthesynchrotronradiationinfraredbeamwasfocusedonthe major intermediates and Cu –CuN clusters wer 3 e chargereflectioncellusingBrukerHyperion3000microscopeequippedwitha×15 2 3 objective.Inthemeasurements,thegapbetweentheworkingelectrodeandthe asymmetric sites that are intensified by CH 3 * adsorbing.</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>The ZnSewindowwascarefullymaintainedontheorderofmicronstoprevent charge-asymmetric sites are responsible for the outstanding excessivewaterabsorption.Allspectrumswerecollectedusingsingle-potential asymmetry ethanol formation.</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Overall, our findings suggest a alterationFTIRspectroscopyandwereacquiredbyaveraging128timesscanwitha 4cm–1resolution,andthebackgroundspectrumswasconductedunderopenstrategy engineering the pre-catalysts to modulate the electron circuitvoltage,thevoltagerangesforconductingmeasurementswere0Vto–1.2V transfer and in-situ generate ultrasmall metal clusters anchored withanintervalof0.1V. onthesubstrateashighdispersionasymmetricsites,whichisthe key factor to facilitate the formation of asymmetric products.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -910,19 +1268,47 @@
           <t>S0313</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" t="n">
+        <v>6</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Therefore, 2.3% which the selectivity of EtOH decreased ~6% following CO RR the CO RR intermediates chemisorbed on dCu O, dCu O/ 2 2 2 2 (Supplementary Fig. 23).</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>TEM image and XRD pattern of spent Ag , and dCu O/Au at different potentials were assessed 2.3% 2 2.3% dCu O/Ag showed that morphology and structure are via in situ attenuated total reflectance infrared absorption 2 2.3% maintained following the stability test (Supplementary Fig. 24). spectroscopy (ATR–IRAS) to determine the mechanism for Given the superior EtOH production on dCu O/Ag , it was boosted EtOH. 2 2.3% consequently assessed in a commercially relevant membrane As is shown in Fig. 5a, b and Supplementary Fig. 29, with the electrodeassembly(MEA)(SupplementaryFig.25).Itwasfound cathode potentialat −0.3V , the ATR–IRAS spectra for these RHE that there is a good, linear relationship between applied current catalysts exhibit several new peaks.</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>These are assigned to andvoltageintheMEA(Fig.4e).TheFEsforallproductstested corresponding intermediates based on independently reported in flow cell electrolyzer were well-reproduced in MEA (Supplestudies (Supplementary Table 4).</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -944,19 +1330,47 @@
           <t>S0314</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" t="n">
+        <v>6</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>The degree of introduced Ag-dependent similar.Therefore,otherpotentialmechanismsondCu O/Ag 2 2 2.3% FEs ofproducts from these catalysts wasassessedunder the same need to be assessed for boosted CO RR performance. 2 currentdensity.AsisshowninFig.4b,c,increasingAgindCu O/ ReactionpathwaysforC H andEtOHproductionaresimilar 2 2 4 Ag leads to a volcano-shape for FE that corresponds with a on Cu surfaces, as they initiate with two adsorbed–CO EtOH reverse-volcano on FE , and contrasts with the monotonously dimerization followed by several steps of protonation and CO decreased FE for C H .</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>This correlation between the amount of dehydration to generate a shared intermediate, * HCCOH3,14. 2 4 modified Ag and FEs for CO and EtOH was observed also with The selectivity between C H and EtOH, is significantly 2 4 other applied currents (Supplementary Fig. 22).</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Common to Cudependent on the relative stabilities of the next-intermediates * based catalysts, the coverage of CO on Cu surface is conducive for EtOH and C H pathways branched from HCCOH on Cu 2 4 to C–C coupling to impact EtOH and C H generation sites3,14,40.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -978,19 +1392,47 @@
           <t>S0315</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" t="n">
+        <v>8</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>ARTICLE NATURECOMMUNICATIONS|https://doi.org/10.1038/s41467-022-31427-9 Fig.5InsituATR–IRASmeasurementandmechanismfordCu O/Ag .InsituATR–IRASobtainedduringchronopotentiometryinapotentialwindow 2 2.3% 0.2to−1.2V foradCu O,andbdCu O/Ag underCO RR.(Areferencespectrumobtainedat0.3V in1MKOHissubtracted).Potential RHE 2 2 2.3% 2 RHE dependenceofratioofc*CO /*CO andd*OC H /*OCCOHobtainedfordCu O,dCu O/Ag anddCu O/Au .eSchematicforboostedEtOH bridge atop 2 5 2 2 2.3% 2 2.3% generationoverdCu O/Ag .Yellow-color,gray,white,orange,red,andazurespheresinthemodelrepresentH,C,O,Cu1+,Cu0,andAgatoms, 2 2.3% respectively. dCu O/Ag (Fig.5d)42,43.Thisisattributedtotheasymmetric proposed (Fig. 5e).</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>At first, the coordinated pure-Cu surface is 2 2.3% C−C coupling induced unbalanced coordination environment, replaced with neighboring Ag atoms with modification by Ag in whichdisruptsthecoordinationsitesforC H intermediates,and Cu O and reduces these to CuAg alloy under CO RR.</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Then, the 2 4 2 2 thereby, stabilizes the EtOH intermediates.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1012,19 +1454,47 @@
           <t>S0316</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" t="n">
+        <v>14</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Reaction energy proles and the corresponding intermediate structures (0 to 7) for the formation of ethanol via the CO RR on the Sn -O3G catalyst.</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>Extended data Fig. 58 shows the detailed free energy proles for 3 to 5. 2 1 Supplementary Files This is a list of supplementary les associated with this preprint.</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Click to download.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1046,19 +1516,47 @@
           <t>S0317</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" t="n">
+        <v>4</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>It is worth noting that no other C2 products (such as ethylene or acetate) were detectable over the entire potential range applied during the CO RR.</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>Compared to state-of-the-art catalysts for electrochemical CO reduction 2 2 to ethanol (Fig. 1d), our Sn-based tandem catalyst shows the best CO -to-ethanol performance. 2 To study the superb CO RR performance to ethanol, the as-synthesized catalyst was carefully 2 characterized by scanning electron microscopy (SEM), transmission electron microscopy (TEM), subangström-resolution high-angle annular dark-eld scanning transmission electron microscopy (HAADFSTEM), X-ray diffraction (XRD), Raman spectroscopy, X-ray photoelectron spectroscopy (XPS) and X-ray absorption spectroscopy (XAS) to reveal the structural information.</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>The SnS /Sn -O3G catalyst 2 1 comprises of two components: vertically-aligned SnS nanosheets (Extended data Figs. 29a) grown on a 2 3D carbon support decorated with atomically-dispersed Sn atoms (Figs. 2d and h).</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1080,27 +1578,55 @@
           <t>S0318</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" t="n">
+        <v>7</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>As a result of forming the strongly bound carbonate species, it hardly generates CO directly except from the recovered catalyst via 3 − 1 intermediate (as shown in Extended data Fig. 55b).</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>The differential charge distribution analysis and Bader charges of 3 determined that the positive charge was higher on the Sn atom, such that bonding between Sn atom and HCOOH (externally added or in-situ produced over SnS ) was favored.</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>With PCET, the carbonyl group in HCOOH* can easily dehydrate to 2 generate Sn-CHO in intermediate 4, with a free energy barrier of 0.52 eV.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>P5:HCOO</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>uncertain</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1122,19 +1648,47 @@
           <t>S0319</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" t="n">
+        <v>7</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>The free energy barrier to C-C bond formation is 0.13 eV, which is much lower than those of Cu-based catalysts (&gt; 1.0 eV) 13,28.</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>Thus, intermediate 6, which contains a Sn-C-C-O quaternary ring, is obtained.</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>As reduction proceeds, with exergonicity of 0.99 eV, the Sn-C bond breaks upon further PCET, then forms the *CH CHOH 3 intermediate (7), followed by PCET and O-C bond cleavage (with a free energy barrier of 0.87 eV), and nally releases CH CH OH from the active site.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1156,19 +1710,47 @@
           <t>S0320</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Zhang,G.etal.EfficientCO electroreductiononfacet-selective 2 facialunitnormalvector,andδisthedeltafunctioncenteredatthe copperfilmswithhighconversionrate.Nat.Commun.12, interface. 5745(2021). 13.</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
         <is>
           <t>Choi,C.etal.AhighlyactivestardecahedronCunanocatalystfor Densityfunctionaltheory(DFT)methods hydrocarbonproductionatlowoverpotentials.Adv.Mater.31, The theoretical calculation was conducted by Vienna ab initio 1805405(2019). simulation package (VASP) with the BEEF-vdW exchange-correla14.</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Chen,Z.etal.Grain-boundary-richcopperforefficientsolar-driven tionfunctional55.Asforthesimulationmodels,webuiltfive-layer electrochemicalCO reductiontoethyleneandethanol.J.Am. 2 Cu(111)-(4×4) slabs with a Butyl Mercaptan and 1-dodecanethiol Chem.Soc.142,6878–6883(2020). moleculartocomparetheeffectofdifferentlengthsofthiolsonthe 15.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1190,19 +1772,47 @@
           <t>S0321</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Choi,C.etal.AhighlyactivestardecahedronCunanocatalystfor Densityfunctionaltheory(DFT)methods hydrocarbonproductionatlowoverpotentials.Adv.Mater.31, The theoretical calculation was conducted by Vienna ab initio 1805405(2019). simulation package (VASP) with the BEEF-vdW exchange-correla14.</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
         <is>
           <t>Chen,Z.etal.Grain-boundary-richcopperforefficientsolar-driven tionfunctional55.Asforthesimulationmodels,webuiltfive-layer electrochemicalCO reductiontoethyleneandethanol.J.Am. 2 Cu(111)-(4×4) slabs with a Butyl Mercaptan and 1-dodecanethiol Chem.Soc.142,6878–6883(2020). moleculartocomparetheeffectofdifferentlengthsofthiolsonthe 15.</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Reller,C.etal.SelectiveelectroreductionofCO towardethylene 2 reaction mechanism.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1224,27 +1834,55 @@
           <t>S0322</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" t="n">
+        <v>5</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0.01 a.u. 2200 2150 2100 2050 2000 1950 1900 Wavenumber (cm-1) coverage or H O content18,46–49.</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>*H and *CO occupy most of the Cu coverage)onthesurface.Theseresultssuggestthatthevariationof 2 surfacesites,resultingindirectcompetitionbetween*Hand*COfor the interface contact state derived from the interfacial wettability surfacesites47.Whenthesurfacemaintainsahigh*COcoverage,the affects both CO and H O transport, which may be a solution for 2 2 corresponding *H coverage will decrease12,18,46,47.</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>According to the simultaneouslytuningkinetic-controlled*COand*H. results of in-situ ATR-SEIRAS spectra (Fig. 3d, e) and in-situ Raman ThelocalCO /HOratioderivedfromwettabilitymayaffectthe 2 2 spectra (Supplementary Fig. 35), higher hydrophobicity indicates coverage of *CO and *H, resulting in the reaction pathways toward higher *CO coverage, thus the corresponding *H coverage is lower. ethylene or ethanol.</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>P1:*COCO; P1:COCO</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1266,19 +1904,47 @@
           <t>S0323</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Performing CO R in acidic elecsurface CO* bindings on the binary sites nearby.</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t>Note that over2 trolytesimprovesCO utilizationbecausecarbonateisdifficulttoform weakened CO*binding (&gt;−0.16eV) on the Cu facets is undesirable19 2 atpH≤415.Itthereforeurgesthedevelopmentofrobustcatalystswith becauseofthedifficultyinformingkeyintermediatesofCOOH*,which highC–Ccouplingactivityandpotentiallycommercialviability. wouldmakeprotonationastherate-limitingstepforC production 2+ InelectrocatalyticCO Rsystems,afundamentalissueistheslow withhighreactionenergies. 2 reactionkineticsof carbon–carbon (C–C) coupling.</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Mechanistically, Accordingly,weusedCO*adsorptionenergyasadescriptorto C–Ccoupling(C–CbondformationbetweenCO*–CO*,CO*–CHO*,or screenaseriesofCu-basedbinaryactivesites(Fig.1b).Consideringa CO*–COH*intermediates)isa(thermo-)chemicalstepthatdoesnot CO*-adsorption-energywindowof~0.40eV,16candidatebinarysites involveelectron/protontransfer.Accordingly,catalystsurfacepolarwere found promising for higher CO -to-C activities (Fig. 1b).</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1300,19 +1966,47 @@
           <t>S0324</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Cu, Zn underreductionconditions.UsinginsituRamanspectroscopy,elecCuZn211 was identified as the most active site, with a small C–C Zn trochemicalhydrodynamicsimulations,andelectrochemicaloperatcoupling barrier and a low limiting potential (Fig. 1e).</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>Microkinetic ing experiments, we determine the key features of intermediate modelling26furthervalidatedtheenhancedactivityoftheCuZnalloy adsorptionandelectrocatalyticenvironmentthatleadtothemarked for CO R to C , with CuZn211 showing the highest theoretical 2 2+ Zn CO RperformancewithimprovedCO utilizationinacidicconditions. activity (Fig. 1f).</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Importantly, the most stable CuZn111 shows sig2 2 Zn nificantlyincreasedC activitycomparedtoCu111,whichenhanced 2+ Results C productionduringextendedCO R.TheHERactivitywasalsocal2+ 2 Mechanisticstudiesandcatalystdesign culatedon(111),(100),and(211)surfacesofCuandCuZn.Ingeneral,a To search for promising catalysts, we set out from a mechanistic worseHERactivitywasobtainedonalltheCuZnsurfacescompared analysisofCO -to-C conversionoverthesimplifiedreactionnetwork withthatonCuduetotheweakerH*binding(SupplementaryFig.7). 2 2+ (Supplementary Fig. 1) and calculated activity trends via density Overall,ourglobalenergyoptimizationschemeindicatedthatalloying functionaltheory(DFT).ThreemajorC–Ccouplingmechanismswere ZnwithCuenablesasymmetricsurfaceCO*bindingsonsurfacebinary considered: CO*–CO* (R5), CO*–CHO* (R6), and CO*–COH* (R7) sites to reduce the reaction energy for C–C coupling, therefore (SupplementaryTable5).Inadditiontoseveralimportantprotonation effectivelypromotingCO -to-C reduction. 2 2+ steps, six reaction pathways were enumerated (Supplementary Tables 5, 6).</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1334,19 +2028,47 @@
           <t>S0325</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RPD RHE thelimitingenergiescalculatedasthemaximumofthereactionenergyofR1and electrochemicalCO 2 Rperformance,wesprayedtheCu x Zn 1−x (x=0.95, 0.85, 0.8) and Cu surfaces at different potentials in a homemade 0.9, 0.85, 0.8, 0.7) model catalysts and commercial Cu catalysts flow-cellsystem(SupplementaryFig.12).AsshowninFig.2c,d,and (Aladdin, Product No.: C103844-10G, 80–100nm) on polytetraSupplementary Figs. 13, 14, characteristic Raman peaks were fluoroethylene (PTFE) substrates.</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
         <is>
           <t>Volcano-shaped curves were observedat~280and370cm−1,attributedtofrustratedrotationand obtainedfortheC Faradaicefficiency(FE).Notably,at150mAcm−2, stretching vibrations of Cu–CO bonds27, at ~1900–2100cm−1, 2+ theC FEoftheCu Zn modelcatalystwas considerablyhigher attributedtostretchingvibrationsofC≡Obonds(bridge-typeCO 2+ 0.9 0.1 than that of the commercial Cu catalyst(66±2% and ~50%, respecat1900–2000cm−1andatop-typeCOat2000–2100cm−1)27,28,andat tively;SupplementaryFig.10andTable10).Further,fortheCu Zn 2800–3000cm−1,attributedtoC–Hstretching29.TheaboveRaman 0.9 0.1 modelcatalyst,theC /C ratioof~11washigherthanthatof~6forthe bandsdisappearedwhenArwasusedinsteadofCO underthesame 2+ 1 2 commercialCucatalyst(SupplementaryFig.11). electrochemical conditions (Supplementary Fig. 13f), confirming Consideringtheaboveresults,weco-sputteredCu y Zn 1−y (y=0.95, that the above observed Raman peaks were representative of CO 0.9,0.85,0.8)catalystsonPTFEgas-diffusionelectrodes.Thethickadsorptiononthesurfaces.RightafterflowingCO ,quickrecovery 2 nessofthesputteredCu y Zn 1−y was~200nm,whichenabledashort of the Cu–CO, C≡O, and C–H stretching peaks were observed, distance for CO 2 diffusion from PTFE to the Cu y Zn 1−y surface. suggesting fast CO 2 R and C–C coupling on Cu 0.9 Zn 0.1 (SuppleRemarkably, the CO 2 -to-ethylene onset potential with the co-sputmentaryFig.13g).ForalltheCuandCu y Zn 1−y surfaces,theRaman tered,best-performingCu Zn (−0.3V )was~0.16Vsmallerthan peakat~370cm−1wasslightlyred-shiftedasthepotentialbecame 0.9 0.1 RHE thatwithpureCuunderthesamereactionconditions(Fig.2a).The more negative, consistent with the electrochemical Stark effect27.</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>TafelslopesforCO -to-ethyleneconversiononpureCuandCu Zn Thepeakat~1900–2100cm−1wasalsoslightlyred-shifted,likelydue 2 0.9 0.1 were167.1and110.9mVdecade−1,respectively,highlightingthatC–C toC≡Odipolestretchingwiththeincreaseinthesurfaceelectric couplingoccurredfasterafterZnincorporation(Fig.2b). field.Importantly,theRamanbandsat~280,370,1900–2100cm−1, We performed in situ Raman studies to explore the interand 2800–3000cm−1 appeared at a more positive voltage for mediate adsorption on the co-sputtered Cu y Zn 1−y (y=0.95, 0.9, Cu 0.9 Zn 0.1 (−0.30V RHE )thanforCu(−0.46V RHE )(Fig.2e),whichis NatureCommunications|( 2023)1 4:1298 3</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1368,19 +2090,43 @@
           <t>S0326</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Volcano-shaped curves were observedat~280and370cm−1,attributedtofrustratedrotationand obtainedfortheC Faradaicefficiency(FE).Notably,at150mAcm−2, stretching vibrations of Cu–CO bonds27, at ~1900–2100cm−1, 2+ theC FEoftheCu Zn modelcatalystwas considerablyhigher attributedtostretchingvibrationsofC≡Obonds(bridge-typeCO 2+ 0.9 0.1 than that of the commercial Cu catalyst(66±2% and ~50%, respecat1900–2000cm−1andatop-typeCOat2000–2100cm−1)27,28,andat tively;SupplementaryFig.10andTable10).Further,fortheCu Zn 2800–3000cm−1,attributedtoC–Hstretching29.TheaboveRaman 0.9 0.1 modelcatalyst,theC /C ratioof~11washigherthanthatof~6forthe bandsdisappearedwhenArwasusedinsteadofCO underthesame 2+ 1 2 commercialCucatalyst(SupplementaryFig.11). electrochemical conditions (Supplementary Fig. 13f), confirming Consideringtheaboveresults,weco-sputteredCu y Zn 1−y (y=0.95, that the above observed Raman peaks were representative of CO 0.9,0.85,0.8)catalystsonPTFEgas-diffusionelectrodes.Thethickadsorptiononthesurfaces.RightafterflowingCO ,quickrecovery 2 nessofthesputteredCu y Zn 1−y was~200nm,whichenabledashort of the Cu–CO, C≡O, and C–H stretching peaks were observed, distance for CO 2 diffusion from PTFE to the Cu y Zn 1−y surface. suggesting fast CO 2 R and C–C coupling on Cu 0.9 Zn 0.1 (SuppleRemarkably, the CO 2 -to-ethylene onset potential with the co-sputmentaryFig.13g).ForalltheCuandCu y Zn 1−y surfaces,theRaman tered,best-performingCu Zn (−0.3V )was~0.16Vsmallerthan peakat~370cm−1wasslightlyred-shiftedasthepotentialbecame 0.9 0.1 RHE thatwithpureCuunderthesamereactionconditions(Fig.2a).The more negative, consistent with the electrochemical Stark effect27.</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
         <is>
           <t>TafelslopesforCO -to-ethyleneconversiononpureCuandCu Zn Thepeakat~1900–2100cm−1wasalsoslightlyred-shifted,likelydue 2 0.9 0.1 were167.1and110.9mVdecade−1,respectively,highlightingthatC–C toC≡Odipolestretchingwiththeincreaseinthesurfaceelectric couplingoccurredfasterafterZnincorporation(Fig.2b). field.Importantly,theRamanbandsat~280,370,1900–2100cm−1, We performed in situ Raman studies to explore the interand 2800–3000cm−1 appeared at a more positive voltage for mediate adsorption on the co-sputtered Cu y Zn 1−y (y=0.95, 0.9, Cu 0.9 Zn 0.1 (−0.30V RHE )thanforCu(−0.46V RHE )(Fig.2e),whichis NatureCommunications|( 2023)1 4:1298 3</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>uncertain</t>
-        </is>
-      </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1402,19 +2148,47 @@
           <t>S0327</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" t="n">
+        <v>8</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Thesingle-passC yieldwascalculatedas(therateofC product 2+ 2+ Theelectrolyteresistancewasmeasuredatopencircuitpotentialina formation(R ))/(theflowrateofCO (f )),asfollows: product 2 CO2 frequencyrangefrom10MHzto0.1Hzwithanamplitudeof10mV.All potentialsversusthereferenceelectrodeswereconvertedtopotenC 2+ yield=ð2R ethylene +2R acetate +2R ethanol +3R n(cid:3)propanol Þ=fCO 2 ×100%, tials versus the reversible hydrogen electrode (V RHE ) using the folð8Þ lowingequations: whereRistherateofC productformation,asdeterminedbygas 2+ V RHE =V Ag=AgCl +0:059×pH+E0 AgCl , ð1Þ chromatographyanalysisoftheproduct.</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>DFTcalculations E0 AgCl ð3:0MKClÞ=0:197Vð25(cid:2)CÞ, ð2Þ The Vienna ab initio simulation package (VASP)40 was used for density functional theory (DFT) calculations.</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>The revised CO waspassedthroughthecathodiccompartmentataconstant Perdew–Burke–Ernzerhof(rPBE)functional41wasusedwiththebasic 2 flowrateof20mLmin−1.ThegaseousCO reductionproductswere projector-augmented wave (PAW) method with a cut-off energy of 2 quantified using gas chromatography (Perkin Elmer Clarus 680). 400eV.Thebulkstructures(Cu,Rh,Pt,andAg)wereoptimizedusinga TheliquidproductswerequantifiedusingNMRspectroscopy(Bruker Monkhorst–Packk-pointof4×4×4,the(211)surfaceswerebuiltfirst AVIII600MHz)anddimethylsulfoxide(≥99.9%,AlfaAesar)wasadded to build the activity trend for CO R, where, in general, metal (211) 2 as an internal standard.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1436,19 +2210,47 @@
           <t>S0328</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" t="n">
+        <v>8</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>The RHE)ofethanolforCO R,whichis0.09Vforethanol39. 2 catholyteofpH1were0.05Msulfuricacid(HSO )and3Mpotassium The C selectivity was calculated as (the rate of C product 2 4 2+ 2+ chloride(KCl)solution,andpHwasadjustedtoaround1byafewdrops formation (R ))/(the rate of total product formation (R )), as product tot of5Mpotassiumhydroxide(KOH).ThecatholyteofpH4were3MKCl follows: solution,andpHwasadjustedtoaround4byafewdropsofH SO . 2 4 ThecatholyteofpH7were3MKClsolution,andpHwasadjustedto C 2+ selectivity=ð2R ethylene +2R acetate +2R ethanol +3R n(cid:3)propanol Þ= around7byafewdropsof1MKOH.ThecatholyteofpH13.5were ðR +R +R +2R +2R ð7Þ CO formate methane ethylene acetate 0.75MKOHsolution.TheanolyteofpH1and4were0.5MH SO ,the anolyte of pH 7 were 1M KHCO , and the anolyte of pH 1 2 3.5 4 were +2R ethanol +3R n(cid:3)propanol Þ×100%, 3 0.75M KOH.</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>Electrochemical impedance spectroscopy (EIS) was measuredtoestimatetheelectrolyteresistanceforiRcompensation.</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Thesingle-passC yieldwascalculatedas(therateofC product 2+ 2+ Theelectrolyteresistancewasmeasuredatopencircuitpotentialina formation(R ))/(theflowrateofCO (f )),asfollows: product 2 CO2 frequencyrangefrom10MHzto0.1Hzwithanamplitudeof10mV.All potentialsversusthereferenceelectrodeswereconvertedtopotenC 2+ yield=ð2R ethylene +2R acetate +2R ethanol +3R n(cid:3)propanol Þ=fCO 2 ×100%, tials versus the reversible hydrogen electrode (V RHE ) using the folð8Þ lowingequations: whereRistherateofC productformation,asdeterminedbygas 2+ V RHE =V Ag=AgCl +0:059×pH+E0 AgCl , ð1Þ chromatographyanalysisoftheproduct.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1470,19 +2272,47 @@
           <t>S0329</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Thus, we opted to use this treatment a significant influence on CORR.</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>For example, by comparing various to obtain sufficient enhancement of the Raman signals. 2 single-crystal surfaces with different surface roughness, we previously Similar to the oxide-derived Cu (OD-Cu) materials, which are showed that undercoordinated Cu sites are required for C formation24. selective for C–C coupling24–27, the as-prepared Cu electrode with a 2 However, it is important to further close this knowledge gap by unravelhigh electrochemical surface roughness factor (14.6; Supplementary ling how Cu coordination and local stress under reaction conditions Fig. 6, electropolished Cu foil as a reference) shows high performance affect the catalytic behaviour and thus the full mechanistic picture.</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>To towards C products and provides the opportunity to detect C–C cou2+ this end, it is required to overcome the challenging low surface coverpling intermediates25.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1504,19 +2334,47 @@
           <t>S0330</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>The specific current densities increase up to at ages of intermediates due to their short lifetimes as well as disentangle least −1.1 V (Fig. 1e), while the Faradaic efficiencies of CORR products 2 the similarities in the vibrational properties of different C–C coupling and H vary strongly with the applied potential (Fig. 1f).</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>The Faradaic 2 intermediates14. efficiencies of C products show a typical volcano dependence on 2+ Here we provide direct spectroscopic evidence of potentialthe applied potential, with a maximum of 65% at about −1.0 V .</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>The RHE dependent CO dimerization and subsequent reduction intermedionset potentials for ethylene and ethanol are about −0.8 V and RHE ates during CORR on a Cu surface by combining insights from in situ −0.9 V , with these products reaching a maximum value at −1.0 V 2 RHE RHE surface-enhanced Raman spectroscopy (SERS) and density functional and −1.05 V , respectively.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1538,27 +2396,55 @@
           <t>S0331</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" t="n">
+        <v>3</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>These peaks appeared RHE x a small peak is detected at 1,070 cm−1, typically assigned to carbonsimultaneously during the time-resolved in situ SERS experiment after ate13.</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
         <is>
           <t>Two new peaks at ∼1,390 cm−1 and ∼1,610 cm−1 appear, which are a potential switch from −0.36 V RHE to −0.96 V RHE (Supplementary Fig. 14). attributed to the symmetric and asymmetric stretching vibrations Concurrently, a broad band in the range of 2,830–2,990 cm−1 appeared, of carboxyl(ate) groups, respectively, based on control experiments which can be attributed to the stretching band of C–H (ref. 12). in Ar-saturated NaClO with 1 mM HCOOH solution (Supplementary 4 Fig. 13) and in Ar-saturated KHCO solution (Supplementary Fig. 11).</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Intermediates responsible for CO RR to ethylene 3 2 At −0.56 V , peaks of CO adsorbed on Cu are detected, with and ethanol RHE vibrational features at ∼280 cm−1, 355–360 cm−1 and 1,970–2,110 cm−1 To confirm the assignment of the vibrational modes detected expericorresponding to the restricted rotation of adsorbed CO (P1), Cu–CO mentally, we reverted to DFT (PBE-D233) through the Vienna Ab initio stretching (P2) and C–O stretching, respectively.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>P5:HCOO</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1580,27 +2466,55 @@
           <t>S0332</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" t="n">
+        <v>4</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Raman spectra were achieved 2 fingerprints.</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
         <is>
           <t>DFT vibrational frequencies for *CO2−, *COCO−, OCHCH (top, left by applying a smearing of 10 cm−1 on each DFT frequency and overlapping the 3 2 to right), *HCOOH, *OCOCO2− and *OCHCH (bottom, left to right) on adsorption resulting peaks.</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Inset: different CORR reaction intermediates, with H atoms s 3 2 sites with different coordination numbers, increasing from orange to black. given in white, O atoms in red and C atoms in black.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
         <is>
           <t>P1;P5</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>P1:*COCO; P1:COCO; P5:HCOO</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>uncertain</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1622,19 +2536,47 @@
           <t>S0333</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" t="n">
+        <v>4</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>We attribute ute the 1,182 cm−1, 1,318 cm−1, 1,453 cm−1 and 1,595 cm−1 signals detected the variations in relative intensities and positions to the substantially at −0.85 V and below to the CCO symmetric stretching, CCO antisymdifferent chemical environment in the absence of predominantly RHE metric stretching, C–C stretching and C–O (or C=C) stretching of co-adsorbed CO, as is the case in CORR.</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
         <is>
           <t>The increasing relative inten2 OCHCH 2 (or OCHCH 3 ) species, respectively (Supplementary Table 7). sity of the band at ∼1,550 cm−1 is probably caused by key intermediAlthough this assignment is based on different independent experiates for ethylene glycol formation, which is the dominant product of ments, we cannot fully rule out that the Raman bands observed might glyoxal reduction at lower potentials20.</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Instead, these signals were also result from (a set of) very similar adsorbates. not observed for ethanol reduction (Supplementary Fig. 21).</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1656,19 +2598,47 @@
           <t>S0334</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" t="n">
+        <v>4</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>The increasing relative inten2 OCHCH 2 (or OCHCH 3 ) species, respectively (Supplementary Table 7). sity of the band at ∼1,550 cm−1 is probably caused by key intermediAlthough this assignment is based on different independent experiates for ethylene glycol formation, which is the dominant product of ments, we cannot fully rule out that the Raman bands observed might glyoxal reduction at lower potentials20.</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>Instead, these signals were also result from (a set of) very similar adsorbates. not observed for ethanol reduction (Supplementary Fig. 21).</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Thus, we In addition, we carried out 13Cor D-labelling SERS experiments reasonably confirmed the detection of a common intermediate along at −0.95 V (Fig. 4a). 13C/12C exchange led to obvious redshifts of the CO, CO and glyoxal reduction route to ethanol, which is *OCHCH.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1690,19 +2660,47 @@
           <t>S0335</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D36" t="n">
+        <v>4</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RHE 2 2 the 1,455 cm−1 and 1,602 cm−1 peaks, in addition to the CO stretching Overall, the presence of CO molecules on the Cu surface during CORR 2 (2,100 cm−1), Cu–CO stretching (358 cm−1) and CO rotation (275 cm−1) is linked to and probably causes the formation of *CO–CO or *CO–COH bands, proving that these peaks are related to the CORR process.</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
         <is>
           <t>Such at about −0.76 V , and then these species further reduce to, for exam2 RHE redshifts were also confirmed by DFT vibrational analysis of O12CH12CH ple, *OCHCH at −0.85 V and −0.95 V . 2 2 RHE RHE and O13CH13CH (Fig. 4b and Supplementary Table 12).</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Water shows 2 a broad O–H bending band at about 1,600 cm−1 (refs. 14,15) (SuppleCu active sites selective for CO RR to ethylene 2 mentary Table 13), limiting the identification of vibrations from other and ethanol species in this regime.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1724,19 +2722,47 @@
           <t>S0336</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" t="n">
+        <v>4</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Such at about −0.76 V , and then these species further reduce to, for exam2 RHE redshifts were also confirmed by DFT vibrational analysis of O12CH12CH ple, *OCHCH at −0.85 V and −0.95 V . 2 2 RHE RHE and O13CH13CH (Fig. 4b and Supplementary Table 12).</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
         <is>
           <t>Water shows 2 a broad O–H bending band at about 1,600 cm−1 (refs. 14,15) (SuppleCu active sites selective for CO RR to ethylene 2 mentary Table 13), limiting the identification of vibrations from other and ethanol species in this regime.</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>In agreement with our assignment, the peak at The potential-dependent formation of C–C coupling intermediates about 1,602 cm−1 still appears after the DO/HO isotope exchange. explains the selectivity trend towards C products observed during 2 2 2+ Besides, the DO/HO exchange negligibly affected the peaks at about CORR.</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1758,19 +2784,47 @@
           <t>S0337</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D38" t="n">
+        <v>5</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>These findings are 2 The C–O stretching frequency of atop CO on Cu depends on the coorfurther supported by Pb underpotential deposition experiments42,43, dination of the underlying metal atom39,40; thus, it can be used as a during which an increased defect site density of CORR at −1.0 V was 2 RHE probe to track the potential-dependent density of different active sites. observed (Supplementary Fig. 22).</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
         <is>
           <t>Finally, adsorbed CO linked to a In principle, the peak shifts to higher wavenumbers for adsorption lower C–O stretching band Raman shift becomes preeminent beyond sites with lower coordination number (although other effects, such −1.1 V , where CH production again significantly increases, in line RHE 4 as dipole coupling, can interfere)40, consistent with DFT simulations with a previous report44.</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Thus, both in situ SERS and cyclic voltammetry (Fig. 5d and Supplementary Table 14).</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1792,19 +2846,47 @@
           <t>S0338</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D39" t="n">
+        <v>5</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Article https://doi.org/10.1038/s41560-024-01633-4 a c 1,2901,4201,605 13CO 2 H 2 O CO 2 D 2 O CO 2 H 2 O 1,305 1,443 2,100 –1.00 V 1,575 –0.95 V –0.90 V 268 354 1,070 1,182 1,320 1,455 –0.85 V 1,200 1,400 1,600 2,045 –0.80 V 275 –0.76 V 358 500 1,000 1,500 2,000 –0.70 V b –0.65 V Assignment N Cu–Cu ν 12C (cm–1) ν 13C (cm–1) ioChem-BD –0.60 V CCO symmetric 6.17 1,184, 1,156, OD-Cu-254 –0.55 V stretching 5.00 1,185 1,158 OD-Cu-297 CCO –0.50 V antisymmetric 5.00 1,323 1,317 OD-Cu-297 stretching –0.40 V C–C stretching 6.17 1,476 1,443 OD-Cu-254 –0.30 V C–O (or C=C) stretching 8.03 1,595 1,543 OD-Cu-263 OCP 900 1,200 1,500 1,800 Raman shift (cm–1) −0.56 V to −0.76 V , the *OCCO intermediate forms on the surface The formation of defects on the Cu surface during CORR, for RHE RHE 2 and evolves to ethylene at −0.76 V .</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
         <is>
           <t>Instead, the *OCHCH key interinstance, adatoms or small Cu clusters with low-coordinated Cu atoms, RHE x mediate is detected from −0.85 V , the observed onset potential for has been experimentally observed via electrochemical scanning tunRHE CORR to alcohols.</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Besides, the ratio of Faradaic efficiencies towards nelling microscopy41.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1826,19 +2908,47 @@
           <t>S0339</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D40" t="n">
+        <v>5</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Finally, adsorbed CO linked to a In principle, the peak shifts to higher wavenumbers for adsorption lower C–O stretching band Raman shift becomes preeminent beyond sites with lower coordination number (although other effects, such −1.1 V , where CH production again significantly increases, in line RHE 4 as dipole coupling, can interfere)40, consistent with DFT simulations with a previous report44.</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
         <is>
           <t>Thus, both in situ SERS and cyclic voltammetry (Fig. 5d and Supplementary Table 14).</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Four Gaussian peak functions hint at the key role of structural defects in tuning the ethylene/ethanol centred at about 2,035 cm−1, 2,075 cm−1, 2,090 cm−1 and 2,100 cm−1 ratio.</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1860,27 +2970,55 @@
           <t>S0340</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D41" t="n">
+        <v>6</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Distorted domains Faradaic efficiency on CO selectivity supports the hypothesis of CH x present deeper s-band states, whereas crystalline sites are characas common precursors for the two products, providing additional terized by positive s-band centres (versus the Fermi energy).</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
         <is>
           <t>The parallel pathways from CO–CH coupling, in line with the recent x s-band equally affects a previously employed descriptor for ethylene/ CHI/CO reduction study20.</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>These undercoordinated distorted sites 3 ethanol competition, the *O binding strength49.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
         <is>
           <t>P6</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>P6:parallel pathway</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1902,19 +3040,47 @@
           <t>S0341</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D42" t="n">
+        <v>6</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>The parallel pathways from CO–CH coupling, in line with the recent x s-band equally affects a previously employed descriptor for ethylene/ CHI/CO reduction study20.</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
         <is>
           <t>These undercoordinated distorted sites 3 ethanol competition, the *O binding strength49.</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Crystalline sites with open the OCHCH-mediated ethanol route (Fig. 6d). 2 Nature Energy | Volume 9 | December 2024 | 1485–1496 1490 ).u.a( ytisnetnI )Am( tnerruC ).u.a( ytisnetnI 900 910 920 N = 4–5 Cu–Cu Raman shift (cm–1) ).u.a( ytisnetnI a b c 0.3 CuI Cu LMM –1.12 V Cu0 Envelope 0.2 –1.0 V –1.04 V 0.1 –0.8 V 0 –1.1 –1.0 –0.9 –0.8 Kinetic energy (eV) d e –0.95 V –0.85 V –0.76 V ×5 –0.56 V fo oitar ycneiciffe ciadaraF enelyhte/lonahte 1,000 cps Potential (V) 0.08 –0.8 V –1.0 V 0.04 0 –0.04 –0.08 –0.2 0 0.2 0.4 1,950 2,100 Potential (V) Raman shift (cm–1) Fig. 5 | Defect-driven mechanisms for CORR to ethylene and ethanol. a, Ratio The Raman data in c are from the same dataset as those in Fig. 2. d, DFT C–O 2 of the Faradaic efficiencies of ethanol and ethylene as a function of the applied stretching wavenumber as a function of the Cu–Cu coordination number, potential. b, Quasi in situ Cu LMM XAES spectra of electrochemically pre-treated decreasing from orange (N = 4–5) to dark brown (N = 7–8). e, Cyclic Cu–Cu Cu–Cu Cu foils after 1 h of CORR at −0.8 V and −1.0 V without air exposure. c, voltammograms of the electrochemically treated Cu foil after 1 h of CORR at 2 RHE RHE 2 Dependence of the C–O stretching band on the applied potential.</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1936,19 +3102,47 @@
           <t>S0342</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D43" t="n">
+        <v>8</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>The electrochemical measurements were performed in a home-built spectro-electrochemical cell made of Teflon and controlled by a BioConclusion logic SP-240 potentiostat.</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
         <is>
           <t>The cell was equipped with a reference On the basis of in situ SERS and DFT simulations, we identified the cruelectrode (leak-free Ag/AgCl, Alvatek), a counter electrode (Pt ring) cial active sites and reaction intermediates responsible for ethylene and and a Cu foil working electrode.</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Typically, a 15 ml CO-saturated 0.1 M 2 ethanol formation in CORR over a Cu surface.</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1970,19 +3164,47 @@
           <t>S0343</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D44" t="n">
+        <v>2</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Cucouldimprovesethyleneperformance.Qiaoetal.23claimedthat Thesurfacevalencestatesofthe as-synthesizedCu NW,AgCu 1 significantly boosted ethanol production could be achieved by the NWandAgCuNWwereanalyzedbyX-rayphotoelectronspectroscopy tailoredintroductionofAgtooptimizethecoordinatednumberand (XPS).ThesurveyXPSspectrashowagradualincreaseoftheAgpeak oxidationstateofsurfaceCusites.However,duetothecomplexityand withincreasingAgcontent(SupplementaryFig.9andSupplementary diversity of the catalyst’s structure, the underlying mechanism of Table3).Thehigh-resolutionO1sXPSspectrumofCuNW,AgCuNW 1 CO RRtoethylene/ethanolintheCu-Agsystemremainsunclear34,36,37. andAgCuNWexhibitsimilarcharacteristicpeaksat530.5and532.4eV, 2 Recently,therapiddevelopmentofsingle-atomcatalysishasopened whicharerelatedtoadsorbedsurfacehydroxide(OH )andadsorbed ads upnewpossibilitiesforconstructingmodelcatalystswithasymmetric water (H O ), respectively (Supplementary Fig. 10)46.</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
         <is>
           <t>As shown in 2 ads catalyticsites38,39.Inparticular,modificationofcopper-basedcatalysts Fig.1fandSupplementaryFig.11,thebindingenergyofAg3ddisplays withsinglemetalatoms,andrationaldesignofcatalystswithdual-or a positive shift from 368.2eV (Ag NW) to 368.4 (AgCu NW) and 1 multi-catalyticsiteshavebeenshownpromisingtoinduceasymmetric 368.3eV(AgCuNW),implyingagraduallydecreasedchargedensityon C-CcouplinginCO RR40–42.However,littleunderstandingaboutthe AgduetoelectrontransferfromAgtoCu47. 2 exactasymmetricC-Ccouplingmechanismisknown.</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Tofurtherdeterminethechemicalstatesandlocalcoordination Inthiswork,viaamodifiedgalvanicreplacementapproach,two environments of Cu and Ag in AgCu NW and AgCu NW, X-ray 1 modelCu-basedcatalystsdecoratedwithAgnanoparticles(AgCuNW) absorptionnear-edgestructure(XANES)andextendedX-rayabsorpand single Ag atoms (AgCu NW) were rationallydesigned and pretion fine structure (EXAFS) measurements were conducted.</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2004,19 +3226,47 @@
           <t>S0344</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D45" t="n">
+        <v>17</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>ARTICLE IN PRESS pivotal role in determining the selectivity between EtOH and C H 11,16,17.</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
         <is>
           <t>The selectivity of Co - 2 4 0.050 Sub-CuS for EtOH in CO ER suggests that subsurface Co doping may alter the bonding mode of 2 *CHCHO, thereby steering the reaction towards the selective production of EtOH.</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>In-situ Fouriertransform infrared (FTIR) spectroscopy was employed to dynamically track the evolution of reaction intermediates, complemented by DFT calculations to explore potential bonding modes of intermediates in the CO -to-EtOH transformation pathway. 2 S S E R P N I E L C I T R A</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2038,19 +3288,47 @@
           <t>S0345</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D46" t="n">
+        <v>18</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>(h) Comparison of the 2 LFB/(HFB+LFB) ratio in in-situ Raman spectra for different catalysts at different applied potential.</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
         <is>
           <t>S (i) Comparison of the *OC /(*OC +*OC ) ratio in in-situ FTIR spectra for different bridge bridge atop S catalysts at different applied potential.</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>(j) Schematic illustration of the underexplored asymmetric E coupling process and ethanol path directed selectivity problem in CO electroreduction, and flow R 2 diagram illustrating the working principles of isotopic tracking of surface-adsorbed intermediates P based on 12C/13C and H/D isotopes in tandem with in-situ FTIR spectra.</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2072,19 +3350,47 @@
           <t>S0346</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D47" t="n">
+        <v>20</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>This observation highlights the directional selectivity of the Co - 0.050 Sub-CuS catalyst for EtOH.</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
         <is>
           <t>The selectivity between EtOH and C H is primarily governed by the 2 4 bonding mode of the protonation intermediate *CHCHO form *CHCO at Cu sites.</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Co -Sub0.050 CuS’s pronounced selectivity for EtOH and the electron transfer mechanism induced by Co doping suggest that Co doping optimizes the electron configuration of Cu sites and changes the bonding form of *CHCHO.</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2106,19 +3412,47 @@
           <t>S0347</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D48" t="n">
+        <v>20</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>The selectivity between EtOH and C H is primarily governed by the 2 4 bonding mode of the protonation intermediate *CHCHO form *CHCO at Cu sites.</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
         <is>
           <t>Co -Sub0.050 CuS’s pronounced selectivity for EtOH and the electron transfer mechanism induced by Co doping suggest that Co doping optimizes the electron configuration of Cu sites and changes the bonding form of *CHCHO.</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Electron transfer from Cu to Co sites decreases the coordination number of Cu sites, thereby enhancing the coordination capacity of Cu and O siteSs and promoting the protonation S of *CHCO to *CHCHO* intermediates in the form of sEurface-O bonds (the right schematic R illustration of Fig. 3f).</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2140,19 +3474,47 @@
           <t>S0348</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D49" t="n">
+        <v>20</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Co -Sub0.050 CuS’s pronounced selectivity for EtOH and the electron transfer mechanism induced by Co doping suggest that Co doping optimizes the electron configuration of Cu sites and changes the bonding form of *CHCHO.</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
         <is>
           <t>Electron transfer from Cu to Co sites decreases the coordination number of Cu sites, thereby enhancing the coordination capacity of Cu and O siteSs and promoting the protonation S of *CHCO to *CHCHO* intermediates in the form of sEurface-O bonds (the right schematic R illustration of Fig. 3f).</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>And the subsequent protonatioPn steps are carried out via adsorbed O atoms.</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2174,19 +3536,43 @@
           <t>S0349</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D50" t="n">
+        <v>22</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>In contrast, on Co-Sub-CuS, the C-Cu bond 1 shows anti-bonding states crossing the Fermi level, indicating electronic instability of the *CHC*OH adsorbed on Co-Sub-CuS.</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
         <is>
           <t>For the *CHCHO* intermediate, anti-bonding orbitals appear at the Fermi level in both the C-Cu and O-Cu bonds at the copper sites of Vs-CuS and Co-Sub-</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>uncertain</t>
-        </is>
-      </c>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2208,19 +3594,43 @@
           <t>S0350</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D51" t="n">
+        <v>23</v>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
         <is>
           <t>ARTICLE IN PRESS CuS catalysts (Supplementary Fig. 71), indicating an unstable electronic structure for the *CHCHO* intermediate.</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Given these observations, the *CHC*OH and *CHCHO* intermediates might need to undergo backward oxidation or forward reduction to achieve a more stable electronic state.</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2242,19 +3652,47 @@
           <t>S0351</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D52" t="n">
+        <v>23</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>ARTICLE IN PRESS CuS catalysts (Supplementary Fig. 71), indicating an unstable electronic structure for the *CHCHO* intermediate.</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
         <is>
           <t>Given these observations, the *CHC*OH and *CHCHO* intermediates might need to undergo backward oxidation or forward reduction to achieve a more stable electronic state.</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Therefore, various theoretical adsorption configurations for *CHCO, *CHC*OH and *CHCHO* on Vs-CuS (Supplementary Figs. 72-74) and Co-Sub-CuS (Supplementary Figs. 75-77) were explored to gain a comprehensive understanding of the adsorption states and reaction selectivity.</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2276,19 +3714,47 @@
           <t>S0352</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D53" t="n">
+        <v>27</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>The asymmetric coupling of OCCOH was triggered by promoting a mixed adsorption configuration of *CO and *CO .</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
         <is>
           <t>Particularly, the electrons transfer from Cu to Co atop bridge induced by subsurface Co doping enhances the oxophilicity of surface metal sites, which in turn facilitates the formation and conversion of *CHCHO* intermediates in the form of surface-O bonds.</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>This mechanism directs the subsequent protonation towards the EtOH pathway, and capturing the transition from *CHCO to *CHCHO*.</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2310,19 +3776,47 @@
           <t>S0353</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D54" t="n">
+        <v>3</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Theoretical N calculations combined with in-situ isotopic spectroscopy validate these views, and the branching I pathway for converting *CHCO to *CHC E HO* is captured.</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
         <is>
           <t>Consequently, in a membrane electrode L C assembly electrolyzer, the optimized Co-Sub-CuS achieves an ethanol Faradaic efficiency of 78.7% I T at a partial current densityR of 550.9 mA cm-2, with stability over 305 h at industrial-level current A density of 700 mA cm-2.</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>These findings provide a rational design for the development of directionally selective catalysts for CO electroreduction. 2</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2344,19 +3838,47 @@
           <t>S0354</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D55" t="n">
+        <v>35</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>A.</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
         <is>
           <t>Goddard, Full atomistic reaction mechanism with kinetics for CO reduction on Cu(100) from ab initio molecular dynamics free-energy calculations at 298 K.</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Proc.</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2378,19 +3900,47 @@
           <t>S0355</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D56" t="n">
+        <v>2</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>The recent in situ/operando surface-enhanced Raman spectroscopic formation of n-propanol is also observed at −0.75 V with a RHE investigations provided initial evidence of the existence of oxipartial current density of ~0.5mAcm −2 in the presence of O , 2 dizedCuspeciesatreducingpotentials21.Amuchlessdiscussed, while no detectable amount of n-propanol is observed at but arguably more important, aspect is whether the oxidized Cu thispotentialintheoxygen-freeatmosphere.Theonsetpotential species, if they indeed exist at the CO RR conditions, contribute of n-propanol in the oxygen-free atmosphere occurs at as 2 to enhanced reactivity of Cu-based catalysts after oxidative negative as −0.90 V (Fig. 1d), and to achieve a similar rate RHE treatments.</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
         <is>
           <t>It is conceivable that Cu oxide and/or hydroxide of ~0.5mAcm −2 requires an additional 250mV overpotential, species are mere spectators during the CO RR, while prei.e.,−1.00V (Fig.1f).UnlikeC products,theformationrate 2 RHE 2 ferentially exposed facets or defects, e.g., located at the grain ofn-propanoldoesnotshowadrasticfurtherenhancementasthe boundarieson themetallic Cusurface, induced by thetreatment O ratio increases from 10 to 20%, suggesting its distinct 2 are the real cause of change in the catalytic performance22–25. chemistry in forming an additional carbon bond after their This has been shown in our recent work in the CO-reduction common rate-determining step of C–C coupling between two reactiononCu26.Thus,establishingadirectcorrelationbetween adsorbed CO molecules29,31,32.</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>The oxygen induced enhancethesurface speciationofCuatreactionconditions andreactivity ment of all C 2+ products is more pronounced at −0.80 V RHE is a frontier in the CO RR research.</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2412,19 +3962,47 @@
           <t>S0356</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D57" t="n">
+        <v>2</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Compared to planar polycrystalline Cu foil electrodes, beneficial effect of oxidative treatments on Cu-based catalysts in these electrodes can effectively improve the mass transport of the CO reduction reaction (CO RR), the mechanisms through dissolvedgasmoleculesinH-cellconfiguration27–29.Toestablish 2 2 whichtheenhancementisrealizedremainatopicofconsiderable the baseline for the co-reduction studies, the CO RR with pure 2 discussion.</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
         <is>
           <t>A key point of debate is whether oxygen-containing CO isconductedin0.1MKHCO (SupplementaryFig.3a),and 2 3 species,e.g.,CuO ,CuO (OH) ,andCu(OH) ,arepresentatthe the results are consistent with the previous reports on polyx x y x CO 2 RRconditions6,7,10–19.Multipleexsituandinsitu/operando crystallineCucatalysts29,30.ThemajorC 2+productsareethylene, characterizations lead to contradicting conclusions6,7,10–17,19.</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>As ethanol, n-propanol, and acetate, and the major C products are 1 ex situ measurements have the potential of exposing the sample methane, CO, and formate.</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2446,19 +4024,47 @@
           <t>S0357</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D58" t="n">
+        <v>3</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Although the isotopic shift when switching from H O to 2 2 electrodesurface,andthusdiminishingtheimpactoftheORRon D Oislargerthanthatestimatedbasedonthereducedmassofa 2 promoting the CO RR. [Cu-]O-H(D)bendingmode(~20cm −1),thisislikelyduetothe 2 presence of solvent.</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
         <is>
           <t>It is reasonable to assume that there is subInsitusurface-enhancedRamanmeasurements.Tounderstand stantial hydrogen bonding between Cu-OH and the H in the the mechanism through which co-electrolysis of CO and O surroundingwatermolecules,whichwillimpactonthefrequency 2 2 boosts the CO 2 RR activity, in situ SERS is employed to identify oftheCu-OHmode.WhenreplacingH 2 OwithD 2 O,wenotonly surface species presenting during the co-electrolysis36.</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>The Cu replace Cu-OH with Cu-OD, but also replacing the surrounding microparticle catalysts employed in this work readily exhibit the H 2 OwithD 2 O,thus thechangeinthereduced mass isexpected surface enhancement of Raman signals, which alleviate the need to be more significant than that without the hydrogen-bonded to introduce SERS-inducing particles37,38, and is consistent with water.Thepossibilityofthisbandat706cm −1correspondingto several recent studies36,37,39.</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2480,19 +4086,47 @@
           <t>S0358</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D59" t="n">
+        <v>5</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Our computational model also consists model structures and results shown in Figs. 4 and 5, hollow-site adsorbed *OH with different coverage.</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
         <is>
           <t>This is respectively31,45,46. −0.5 V (i.e., equivalent to −0.9 V ) is because *OH is most stable on hollow sites at the negative SHE RHE chosen as the potential in our calculations.</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Cu(100) facet is potentials described by the VASPsol model.</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2514,19 +4148,47 @@
           <t>S0359</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D60" t="n">
+        <v>8</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Angewandte Research Articles Chemie Figure7.</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
         <is>
           <t>Operandosurface-enhancedRamanspectraofa)CuONCs,b)3-Ag/CuO,andc)5-Ag/CuOatopencircuitpotential(ocp)andunder 2 2 2 differentappliedpotentialsinCO-saturated0.1mKHCO.AllpotentialsaregivenwithreferencetoRHE. 2 3 From the ex situ and operando studies performed under *CHCHOþHþþe@!*CHCHO!CHCHO ð1Þ CORR we gained a detailed insight into the structural 2 3 3 2 evolutionoftheAgNP-decoratedCu 2 ONCcatalysts.Intheir *CH 3 CHOþ2Hþþ2e@!C 2 H 5 OH ð2Þ as-prepared state, the CuONCs as well as the AgNP2 decorated samples mainly consist of Cu 2 O, with some If*CH 3 CHOcoupleswithanother*CO,propionaldehyde contribution from CuO.</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>During CO 2 RR, Cu 2 O is partially [Eq.(3)]and1-propanol[Eq.(4)]canbeformed. reduced to metallic Cu, while the contribution of CuO vanishes.</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2548,19 +4210,47 @@
           <t>S0360</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D61" t="n">
+        <v>3</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>The pathway for C 2+ products26–28 is ference, 0.31eV, of *COCO over Cu(111) and Cu(100), indicatillustratedinFig.2a.SolidexperimentalresearchesshowthatCO ing the decreased intercept is merely attributed to the additional 2 electroreduction to multi-carbon products isindependent on the stabilizing effect for *COCO intermediate at square-like sites. standard hydrogen electrode (SHE) scale and C–C coupling step ReflectedinreactionenergyofC–Ccouplingprocess(Fig.2c),the that does not involve proton transfer is considered as rateaverage reaction energy on square sites is 1.27eV, 0.36eV lower determiningstep(RDS)29,whichmeanstherateofC–Ccoupling thanthatonnon-squaresites.Therefore,square-likesitesarethe determines the whole activity for C 2+ products over OD-Cu most potential candidates to serve as active sites for C–C catalysts.</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
         <is>
           <t>Both vibrational spectra30,31 and kinetic models32,33 coupling. reveal that *CO is the main intermediate on Cu surface under Further analysis found that these square sites have different reduction conditions.</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Considering that C 2+ pathway displays a localstructures.Therefore,weclassifiedthesesitesintofourtypes: pH independent on SHE scale, 2*CO dimerization is thus the planar-square (p-sq), step-square (s-sq), concave-square (cc-sq) most accepted form for C–C coupling on copper surface34. and convex-square (cv-sq). p-sq sites are the Σ3 grain boundary )Ve( ygrenE noitcaeR non-square sites square sites selected square sites 1.63eV 1.27eV Average E(*CO) (eV) 1.2 1 0.8 0.6 0.4 0.2 0 -0.2 )Ve( ygrenE noitcaeR d 1.2 1 0.8 0.6 0.4 0.2 0 (111) (100) (221) p-sq s-sq cc-sq cv-sq )Ve( reirraB noitcaeR 0.4 0.2 0 -0.2 -0.4 -0.6 -1.1 -1 -0.9 -0.8 -0.7 -0.6 -0.5 (111) (100) (221) p-sq s-sq cc-sq cv-sq )Ve( )OCOC*(E ARTICLE NATURECOMMUNICATIONS|https://doi.org/10.1038/s41467-020-20615-0 a b c non-square sites square sites selected square sites y=1.82x+1.48 planar-square step-square y=1.85x+1.14 concave-square convex-square Average E(*CO) (eV) e f g p-sq s-sq cc-sq cv-sq side view top view Fig.2IdentificationofC–Ccouplingactivesites.aReactionpathwayforC 2+productsinCO2R.bTheadsorptionenergyof*COCOasthefunctionofthe averageadsorptionenergyoftwoadsorbed*CO.cReactionenergy(2*CO→*COCO)asthefunctionoftheaverageE(*CO)onthesesites.dDFTperiodic slabmodelsoffoursquare-likesites.e*OCCOconfigurationsonthesefoursites(solventmoleculeshavebeenremovedtoshowtheadsorbate configurations).fReactionenergiesandgbarriers(2*CO→*COCO)ondifferentDFTslabmodelsunderappropriateelectrochemicalinterface.Colorcode: brown-Cu;yellow-Cuinsquare-likesites;gray-C;red-O.</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2582,27 +4272,55 @@
           <t>S0361</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D62" t="n">
+        <v>3</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>We then selected another 15 square sites are some obvious steps, which resemble Cu(S)-[n(111)×(111)] from OD-Cu surfaces to verify this tendency.</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
         <is>
           <t>Not surprisingly, step sites, where one atomic height of (111) step is introduced these square sites can efficiently stabilize the *COCO interintoseveralatomicrowsof(111)terrace.Moreover,afewdefects mediate as well.</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Two disparate scaling relationship can be likegrainboundariesandvacanciesexist(SupplementaryFig.13). obtained between the average adsorption energy of two binding Up to now, authentic OD-Cu surface structures are obtained *CO (E(CO)) and coupled intermediate *COCO (E(COCO)) on based on NN-MD simulation of the whole reduction process. the non-square sites and square sites.</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t>P1:*COCO; P1:COCO</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>uncertain</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2624,19 +4342,47 @@
           <t>S0362</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D63" t="n">
+        <v>3</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Moreover, these two relaToimprovetheactivityandselectivityforC 2+productsofthe tionshipsalmostsharethesameslopebuthavea0.34eVintercept catalyst, it is crucial to understand the nature of the active sites difference.</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
         <is>
           <t>This value is very close to the adsorption energy difpresented on Cu catalyst.</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>The pathway for C 2+ products26–28 is ference, 0.31eV, of *COCO over Cu(111) and Cu(100), indicatillustratedinFig.2a.SolidexperimentalresearchesshowthatCO ing the decreased intercept is merely attributed to the additional 2 electroreduction to multi-carbon products isindependent on the stabilizing effect for *COCO intermediate at square-like sites. standard hydrogen electrode (SHE) scale and C–C coupling step ReflectedinreactionenergyofC–Ccouplingprocess(Fig.2c),the that does not involve proton transfer is considered as rateaverage reaction energy on square sites is 1.27eV, 0.36eV lower determiningstep(RDS)29,whichmeanstherateofC–Ccoupling thanthatonnon-squaresites.Therefore,square-likesitesarethe determines the whole activity for C 2+ products over OD-Cu most potential candidates to serve as active sites for C–C catalysts.</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2658,19 +4404,47 @@
           <t>S0363</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D64" t="n">
+        <v>4</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>On p-sq and cv-sq sites (Fig. 3a, b), the instabilityof*O,therebyfurtherhinderingtheethylenepathway cleavage of C–O bond to form C H is thermodynamic favored (Fig. 3f).</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
         <is>
           <t>Based on the analysis above, we elucidated how the 2 4 compared to the protonation of α-C to form *CH CHO intergeometry of C–C active sites affects the bifurcation pathway, 3 mediate.</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Conversely, s-sq site shows strong thermodynamic resulting in the difference of the selectivity for C 2+ products. tendency for further hydrogenation, thus inhibiting the C H Furthermore,wecanproposethatthekeytogeneratingethanolis 2 4 pathwayandmeanwhilepromotingalcoholsproduction(Fig.3c). that square-like sites coupled with low coordinated sites, where Fig.3Identificationofproduct-specificactivesites.Energyprofiletoformethylene(blueline)andethanol(orangeline)foraplanar-squaresite,b convex-squaresite,andcstep-squaresite.dBlue:TherelationshipbetweenthebondlengthofC–OinadsorbedCH CHOandthedifferenceofGibbs-free 2 reactionenergyofC–Oscission(ΔG(C–O))andhydrogenation(ΔG(+H)).Orange:TherelationshipbetweenthebondlengthofC–Oinadsorbed CH CHOandtheICOHPofC–Obond.eGeneralcoordinationnumberandadsorptionenergyof*CH CHOonthesethreeactivesites.fAdsorptionenergy 2 3 of*Oonthesethreeactivesites. 4 NATURECOMMUNICATIONS| (2021) 12:395 |https://doi.org/10.1038/s41467-020-20615-0|www.nature.com/naturecommunications</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2692,19 +4466,47 @@
           <t>S0364</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D65" t="n">
+        <v>21</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>coupling.[43,44] This is consistent with previous studies where it has been confirmed that the intensity ratio of P1 and P2 peaks are potential dependent and higher P2/P1 Raman peak ratios are linked to a higher C-C coupling and C products formation.[43] Furthermore, our in-situ 2+ Raman spectroscopy results show a higher intensity P3 (*C-O stretching) peak of MoP-Im compared to MoP catalyst at the potential of -0.5 V indicating a high concentration/coverage of adsorbed *CO intermediates on the surface of MoP-Im.</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
         <is>
           <t>These results reveal that the high number of adsorbed *CO intermediateson the surface and the higher binding strength of *CO intermediates on the Mo atoms in presence of the Im are the main reasons for a greater C-C coupling and thereby a higher C H OH production for MoP-Im compared to MoP catalyst. [44] 2 5 4.</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Conclusions In summary, we have synthesized and tested the electrocatalytic performance of the MoP-Im co-catalyst for CO RR in a hybrid electrolyte of 3M KOH and 3M KCl.</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2726,19 +4528,47 @@
           <t>S0365</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D66" t="n">
+        <v>3</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Soc. 2017, 139, 11277–11287. https://doi.org/10.021/jacs.7b06765.</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
         <is>
           <t>Demonstrates the impact of the choice of alkali metal cation on the C selectivity of 2+ electrochemical CO reduction on Cu catalysts, demonstrating that alkali cations with smaller 2 hydrated radii pack more tightly in the outer Helmholtz plane and stabilize intermediate adsorption.2 (3) Kim, C.; Weng, L.</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>C.; Bell, A.</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2760,19 +4590,47 @@
           <t>S0366</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D67" t="n">
+        <v>6</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>The coexistence of metallic and oxidized Cu species is also Gas products were detected and quantified after 1 min and every 15 min the key factor for enhanced ethanol formation.</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
         <is>
           <t>As predicted by by online gas chromatography (GC, Agilent 7890B), equipped with a thermal density functional theory modelling11,34,35 and corroborated also conductivity detector and a flame ionization detector.</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Liquid products were analysed after each measurement with a high-performance liquid chromatograph by recent experimental infrared spectroscopy and in situ XAS (Shimadzu Prominence), equipped with a NUCLEOGEL SUGAR 810 column and data36, the asymmetry between CO adsorption energies on metala refractive index detector, and a liquid GC (Shimadzu 2010 plus), equipped with a lic and oxidized copper sites facilitates CO dimerization and is fused silica capillary column and a flame ionization detector.</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2794,19 +4652,47 @@
           <t>S0367</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D68" t="n">
+        <v>2</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>HCOOH (assuming the same type/number of active sites were engaged).Inthisvein,thereshouldbemoreelectrontransferinvolved Results in CO RR catalyzed by Hex-2Cu-O and Oct-2Cu, resulting in more 2 Catalystssynthesisandcharacterization deeplyreducedproductsof&gt;2e−.Inaddition,allthecompoundcataSyntheses of the bicentric copper complexes, denoted as HexlystsshowsignificantlyhigherLSVcurrentdensitythanthatoftheKB 2Cu-O, Hex-2Cu-2O and Oct-2Cu in Fig. 1a–c, respectively, are aloneinCO -saturatedelectrolyte,confirmingthatKB,asaconductive 2 based on the ring expansion of porphyrins following previous agent,doesnotaffecttheperformanceevaluationofthecatalysts. reports (Supplementary Fig. 1)22–25.</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
         <is>
           <t>Their chemical structures are Inthecontrolled-potentialelectrolysis(CPE)from–0.9to–1.5V confirmed by UV–Vis (Fig. 1d) and Mass spectroscopy (Supple- (vs RHE without iR correction, all potentials are referenced to this mentary Figs. 2–4), matching well with the literature results23,24 format hereafter unless specifically noted), Hex-2Cu-O produces and theoretical values.</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>For Hex-2Cu-O, each of the two copper mainlyCOandformateatlowoverpotentials(Fig.2a).Startingfrom ions is bound to one bridging meso-oxygen atom and three pyr- −1.1V and beyond, C products including ethylene, ethanol and n2+ rolic nitrogen atoms in a distorted quadrilateral configuration. propanolconstitutethemainCO RRproducts.Inparticular,at−1.2V 2 The central Cu–O–Cu bonding fights against the tension of the thetotalFaradaicefficiency(FE)ofmulti-carbonalcoholsincreasesto expandedporphyrin,resultinginagabledstructurewithaCu–Cu 50.8%(ethanol:32.5%;n-propanol:18.3%),whichhasbeenrarelyseen distanceof3.7Å(Fig.1a).InHex-2Cu-2O,thedoublyN-confused intheliterature(SupplementaryTable2).At−1.3V,thetotalFEofC 2+ hexaphyrinprovidestwocarbonyloxygenstoallowbothcopper products reaches to its maximum of 71% (Supplementary Fig. 6). ions to be independently anchored by the surrounding three N Afterwards,boththeFEsofethanolandn-propanoldecreases,whereas and one O atoms, also in a square-planar geometry but with theFEandpartialcurrentdensityofethylene continuallyrise (Supmilder Cu-O strain.</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2828,19 +4714,43 @@
           <t>S0368</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D69" t="n">
+        <v>4</v>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
         <is>
           <t>120 H Fromate CO CH 2 2 4 Methanol Ethanol n-Propanol 100 80 60 40 20 0 -1.5 -1.4 -1.3 -1.2 -1.1 -1.0 -0.9 electrochemically stable than Hex-2Cu-2O, and hence the CO RR spectraofOct-2Cubeforeandafterelectrolysisdisplayasimilartrend 2 activityoftheformermusthavecomefromitsmutatedstructure.For to that of Hex-2Cu-O, indicating thatCu2+ inthe moleculewas also Oct-2Cu,post-electrolyticMSdidnotdetectanysignalsfromtheorireduced to Cu+/Cu0 (Supplementary Fig. 18).</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>No Cu2+ state was ginalmacrocycles(i.e.Oct-2CuorOctaphyrin)otherthanabunchof observed in the Cu 2p spectrum of Oct-2Cu after electrocatalysis fragmentsbelowm/z=1100(SupplementaryFig.12).Thisindicatesthe (SupplementaryFig.19).FurtherintheAugerCuLMMspectra,postconjugatedoctaphyrinringofOct-2Cucanbefullyrupturedduring electrolyticHex-2Cu-Ofeaturesabroadpeakthatcanbedecoupledto electrolysis. coordinatedCu2+(572.2eV)andsuperficiallyoxidizedCuδ+(569.8eV) The structural mutation of Hex-2Cu-O was also witnessed by species,whereaspost-electrolyticOct-2CushowsmajorlythesuperUV–vis spectroscopy.</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2862,27 +4772,55 @@
           <t>S0369</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D70" t="n">
+        <v>6</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>As for Oct-2Cu, the attendtotheC–Ccouplingreactionstoformmulti-carbonproducts, staggeredporphyrinligandsthatalsocreateintramoleculartension whichhavebeenreportedinmanypreviousstudies16,37.Meanwhile,the makeitboththermodynamicallyandelectrochemicallylessstable peakshowsaredshiftwithincreasingbias,whichisascribedtothe andcouldfallapartundernegativepotentials.Theseargumentsare Starkshiftcausedbystrongelectronicinteractionbetween*COand well supported by cyclic voltammetry (CV) taken in Ar-saturated theunder-coordinatedmetalcluster38.Thepeakslocatedat1560cm−1 electrolyte (Supplementary Figs. 27 and 28).Hex-2Cu-2O shows a and1436cm−1growingconspicuouslywithdecreasingpotentialcanbe similar voltammogram to that of free-base hexaphyrin without designated to the C-O vibration of adsorbed *OC–CO(H), a strong notableCuvalencechangeinthepotentialrangebetween−0.8and evidence for the direct CO-CO dimerization on Cu clusters39.</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
         <is>
           <t>As 1.2V(SupplementaryFig.27),attestingtoitsstableconfiguration. reportedinpreviousstudies13,16,oneofthemostprobablerate-limiting BothHex-2Cu-OandOct-2Cuexhibitprominentredoxfeatureson stepsforgeneratingC intermediatesisthe*COdimerization,whichis 2 bothcathodicandanodicscans,inaccordancewiththeCuvalence greatly facilitated by concentrated CO adsorption on underchangeobservedbyinsituXAFS(SupplementaryFig.28).Specificoordinated Cu sites.</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>More importantly, the growing peak at cally,thecathodicpeakat−0.39VforHex-2Cu-Ocanbeascribedto 1360cm−1 is ascribed to the stretching of surface-bound *OCH CH 2 3 thereductionCu2+toCu+/Cu0,asconfirmedbytheex-situXPSCu2p species40,whichisconsideredakeyintermediateintheC pathwayto 2+ spectratakenatdifferentbias(SupplementaryFig.29).Theother form alcohols.</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="L70" t="inlineStr">
         <is>
           <t>P1:*CO dimerization; P1:CO dimerization</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>uncertain</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2904,19 +4842,47 @@
           <t>S0370</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="D71" t="n">
+        <v>6</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>In stark contrast, both the in situ XANES and FT-EXAFS oxygen and is fully fragmented.</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
         <is>
           <t>Based on this cognition, we next spectratakenonHex-2Cu-2OexhibitminimalchangeofCuoxidation proceed to unravel how such a complex structure of partially andcoordinationstatesfrom−0.9to−1.5V(Fig.3f,i),evidencing, reducedHex-2Cu-Oworktoproducealcoholsasthemajorproduct onceagain, its electrochemical stability duringCO RR.</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Thein situ inCO RR. 2 2 XASspectraofOct-2CualsotestifythereductionofCu2+toCu0under To elucidate the synergy from the Cu clusters and partially negativebias(Fig.3g,j).At−1.5V,boththespectralfeaturesofXANES reducedHex-2Cu-Ocomplexesinyieldingmulti-carbonproducts,we andFT-EXAFSwellmatchthoseofthecopperfoilwithoutdiscernsoaked the Hex-2Cu-O electrode in ethanol to remove the organic able Cu–N signals, further supporting the view that Cu clusters phaseafterCO RRat−1.2V.Asaresult,thecatalystremainedonthe 2 dominate the post-electrolytic Cu species, which coincides earlier electrodeshouldcomprisemajorlyCuclusterssupportedonKB,as XPSobservations. evidenced by EDXimages before and after soaking (Supplementary SimilarstructuralevolutionofHex-2Cu-Owiththeemergenceof Figs. 30, 31).</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2938,19 +4904,47 @@
           <t>S0371</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="D72" t="n">
+        <v>8</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>The reaction pathways are 2 5 2 4 3 7 In the existing reports of organometallics-derived copper catalysts, summarized in Fig. 5c; a more detailed thermodynamic profile metalliccopperhasbeenoftenperceivedastheonlymotifresponsible regarding all reaction intermediates is given in Supplementary forCO reduction42,43.However,inthecurrentcomparativestudyboth Tables6–8.FortheC pathways(blueandblack),the*COcouplingand 2 2 the characterization results and control experiments suggest there subsequentproton-coupledelectrontransfer(PCET)toform*OCCOH exists a synergy between the Cu clusters and partially reduced (2*CO+H++e− → *OCCOH) show the maximum uphill free energy O-containing hexaphyrin complexes in promoting C production, change (ΔG).</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
         <is>
           <t>This step isthe potential-determine step (PDS) with a 2+ especially the alcohols.</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Although the exact structure of this hybrid limiting potential(U )of–0.92V.Thesubsequentreductionof limiting complexisdifficulttocharacterizeexplicitly,westillbuildastructure *OCCOHonR-Hex-2Cu-O/Gproceedsintwomajorpathways(Fig.5c), model,basedonalltheexperimentalevidencegainedaboveaswellas including:(1)C H pathway(black)viatheformationofintermediate 2 4 thebestscientificguess,fortherestructuredHex-2Cu-Obyplacinga *HOCCOH, and (2) C HOH pathway (blue) via the formation of 2 5 Cu cluster adjacent to the partially reduced Hex-2Cu-O molecule *OCHCOH.</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2972,19 +4966,47 @@
           <t>S0372</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D73" t="n">
+        <v>2</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>We find that the which step in each pathway the C–O bond breaks most easily and distinct pH effect on the C Oxy/HC selectivity stems from the consequently identify the product specificity of the different 2 selectivity-determining steps (SDSs) in each pathway having pathways. different proton-electron transfer (PET) numbers with water as the proton source.</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
         <is>
           <t>This insight allows us to propose two simple The CHCOH pathway.</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Among the three possible protonation descriptorsfortheC Oxy/HCselectivityonagivenmaterial-the steps, the protonation of the hydroxyl group in CHCOH* to 2 adsorptionfreeenergiesofC*andOH*.Theseenergiesserveasa produce water and CCH* is the most kinetically favorable measureofthecarbophilicityandoxophilicityofthesurface.The pathway (Fig. 2f and Supplementary Fig. 6).</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3006,19 +5028,47 @@
           <t>S0373</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D74" t="n">
+        <v>2</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>This insight allows us to propose two simple The CHCOH pathway.</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
         <is>
           <t>Among the three possible protonation descriptorsfortheC Oxy/HCselectivityonagivenmaterial-the steps, the protonation of the hydroxyl group in CHCOH* to 2 adsorptionfreeenergiesofC*andOH*.Theseenergiesserveasa produce water and CCH* is the most kinetically favorable measureofthecarbophilicityandoxophilicityofthesurface.The pathway (Fig. 2f and Supplementary Fig. 6).</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Cheng et al. also degreeof carbophilicity isshowntoprimarily guide theC Oxy/ suggested the predominance of CCH formation through 2 HC production.</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3040,19 +5090,47 @@
           <t>S0374</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D75" t="n">
+        <v>4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>ARTICLE NATURECOMMUNICATIONS|https://doi.org/10.1038/s41467-022-29140-8 Fig.2Freeenergydiagrams(FEDs)ofCORonCu(100)atU =−0.73V(pH7).aTSstructuresofCHCO-H(TS1),CHC-HO(TS2),andOCCH-H RHE (TS3)protonation.FEDsshowingbthemajorCHCOHpathwaytowardsethylene(red)andethane(yellow),ctheminorCHCOHpathwaytowards ethylene(red)andacetylene(brown),dtheOCHCHpathwaytowardsethanol(blue)andacetaldehyde(navy),andetheCH COpathwaytowardsacetic 2 acid(green)andanintermediate(blue)leadingtotheothertwoC Oxyproducts.Thecoloredsquaresinbanddhighlightregionswherekeycompeting 2 reactionstepsappearfrombranchingpathwaysasillustratedinFig.1:fCHCHOHformationfromCHCOH*(purple),possiblyleadingtoC Oxysand 2 gethyleneformationfromOCHCH *(purple)asproposedbyCalle-Vallejoetal.26andbasedonlyonthethermodynamicstabilitiesofsurfacespecies. 2 ImportantTSstructures,CHCOH-H(TS4)andCHC-HOH(TS5)protonationareshowninf,andOCH-HCH (TS6),CH CHO-H(TS8),andOCHCH -H 2 2 2 (TS9)protonation,aswellasC–OscissionofOCH CH *(TS7)areshowning.Electrochemicalprotonationstepsareshownassolidlineswhilechemical 2 2 processesareshownasdashedlines.AllenergiesintheFEDsarereferencedtoCO(g),H (g),andH Obasedonthecomputationalhydrogenelectrode 2 2 (CHE)model.Thevaluesinparenthesesinb–grepresenttheΔG atU =−0.73V(pH7).SourcedataareprovidedasaSourceDatafile. a RHE via surface hydrogenation35.</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
         <is>
           <t>Since the C–O bond breaks easily absence of C HC products, acetylene and ethane, observed 2 through CHCOH-H protonation, the CHCOH pathway is conexperimentally may be attributed to the slower H-CCH protonasequently identified to exclusively produce C HCs.</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Once the tion and CCH -H protonation steps compared to the steps 2 2 CCH* isformed, a seriesofCH x CH y+1 * intermediates(x, y&gt;0) towards ethylene, i.e.</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3074,19 +5152,47 @@
           <t>S0375</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="D76" t="n">
+        <v>5</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Experimental values protonationstepsforC Oxy/HCproducts,wehavedevelopeda were adopted from the literature where a broad range of Cu 2 mean-field microkinetic model that accounts for adsorbatecatalysts and reactor types were investigated.</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
         <is>
           <t>We classify the Cu adsorbate interactions (see details in Supplementary Note 6)25. catalysts into pcCu electrodes4,6,20,21,41, OD-Cu electrodes6,16,41, Given the intrinsic DFT errors (±0.15eV) on barriers and single-crystalCuelectrodes13,andhigh-roughness-factor(RF)Cu intermediate energies and the uncertainties brought by the electrodes (mostly derived from oxide)14,15.</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>For a fair comparparameterization and the varying solvent structures, the microison,weonlyconsideredtabulatedliteraturevalueswithproduct kinetic model only serves as a tool for qualitative comparison distribution and CO R in 0.1M KHCO electrolyte or COR in 2 3 with experimental trends in activity and selectivity. 0.1MKOHelectrolyteforFig.3c.The0.1Mcationconcentration NATURECOMMUNICATIONS| (2022) 13:1399 |https://doi.org/10.1038/s41467-022-29140-8|www.nature.com/naturecommunications 5</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3108,19 +5214,47 @@
           <t>S0376</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D77" t="n">
+        <v>7</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>(cid:3) ðβOCCH(cid:1)H(cid:1)βCHCOH(cid:1)H(cid:1) a 1ÞeU RHE þð4GC a; H 0 a COH(cid:1)H(cid:1)4G a O ;0 CCH(cid:1)HÞ CHCOH-HTS exhibits a significantly higher DSC than at pH7 r C2HC k B T when U &gt;−0.4V.</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
         <is>
           <t>Such a shift with pH in the SDS is ð1Þ RHE analogous to the shift in the RDS for the COH pathway to whereas on the left leg we find ΔGCHCOH(cid:1)H &lt;ΔGCHCO(cid:1)H, such produce methane (Supplementary Fig. 3)35.</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Because of the a a additional protonation step required to produce CCH* + H 2 O tha t ! fromCHCOH*,increasing pHsuppresses theCHCOHpathway ln r C2Oxy (cid:3) ðβOCCH(cid:1)H(cid:1)βCHCO(cid:1)HÞeU RHE þð4G a C ; H 0 CO(cid:1)H(cid:1)4G a O ;0 CCH(cid:1)HÞ at the same absolute potential (vs. standard hydrogen electrode, r k T U ) and consequently yields higher C Oxy/HC selectivity at C2HC B SHE 2 ð2Þ low overpotentials (Supplementary Fig. 13).</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3142,19 +5276,47 @@
           <t>S0377</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="D78" t="n">
+        <v>7</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Such a shift with pH in the SDS is ð1Þ RHE analogous to the shift in the RDS for the COH pathway to whereas on the left leg we find ΔGCHCOH(cid:1)H &lt;ΔGCHCO(cid:1)H, such produce methane (Supplementary Fig. 3)35.</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
         <is>
           <t>Because of the a a additional protonation step required to produce CCH* + H 2 O tha t ! fromCHCOH*,increasing pHsuppresses theCHCOHpathway ln r C2Oxy (cid:3) ðβOCCH(cid:1)H(cid:1)βCHCO(cid:1)HÞeU RHE þð4G a C ; H 0 CO(cid:1)H(cid:1)4G a O ;0 CCH(cid:1)HÞ at the same absolute potential (vs. standard hydrogen electrode, r k T U ) and consequently yields higher C Oxy/HC selectivity at C2HC B SHE 2 ð2Þ low overpotentials (Supplementary Fig. 13).</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>This shift also rationalizes the inverse Volcano shown in Fig. 3c.</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3176,19 +5338,47 @@
           <t>S0378</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D79" t="n">
+        <v>2</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>The low2 L 2 P 2 forthepurposeofbondingoxyhydrocarbons. coordinated Cu /Cu O achieved a C alcohols faradic efficiency L 2 2+ Severalstrategiescanimprovetheselectivityofoxyhydrocarbons (FE )of64.15±1.92%withthecorrespondingenergyefficiencyof alcohols inCER,includingthehighconcentrationoflocal*COaroundtheactive ~39.32%.Inaddition,astableC alcoholsfaradaicefficiencyof&gt;50% 2+ sites14,15,dopingmodificationofcoppercatalystswithheteroatoms16,17, was also obtained during a continuous 50h chronopotentiometry building of crystal defects and low coordination of copper12,18,19. experiment.Ourresearchprovidesaplatformfortherationaldesign Effectively, the coverage of *CO can be facilitated on the lowof low-coordinated Cu–Cu O Mott–Schottky catalysts and analyzes 2 coordinatedCusitesofoxide-derivedCu,leadingtoitssubsequent thekeyelementsforefficientsynthesisofC alcohols. 2+ hydrogenationinto*COH,whichisessentialforthecouplingofOC −COH20,21.Forexample,LianggroupreportedafragmentedCucatalyst Results withabundantlow-coordinatedsitesbyelectrochemicalreconstrucSynthesisandcharacterizationofCu L /Cu 2 Onanoparticles tion ofB-dopedCu O,whichexhibited aC products faradaiceffiThe Cu /Cu O catalysts were synthesized using a simple electro2 2+ L 2 ciencyof77.8%at300mAcm−2(seeref.19).Theoreticalcomputations chemical reconstruction strategy on Cl–Cu O nanoparticles (see 2 havedemonstratedthatthe*CObindingscouldbestrengthenedon detailsin“Methods”,SupplementaryFigs.1–4).TheCu /Cu Ocatalysts L 2 low-coordinated copper sites and prefer to coupling with *COH are designed to function as a Mott–Schottky catalyst of Cu/Cu O, 2 insteadof*COdimerization22.Moreover,theincorporationofhalide which generates enhanced rectifying interfaces between electronspecies and the creation of oxygen vacancy also contribute to the deficientmetalandelectron-richregionbecauseofthedifferencein formationoflow-coordinatedmetalandthecontrolledgenerationof work function (Fig. 1A).</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
         <is>
           <t>The rectifying interface effect of Cu–Cu O 2 intermediates23,24.Sunandco-workerintervenedthebehavioroflowMott–Schottky catalyst adjusts the electronic densities through coordinationchlorideion(Cl−)adsorptiononthesurfaceofasilver interfacial charge exchange, resulting in reduced adsorption resishollowfiber(AgHF)electrodein3MKClelectrolyte,whichresultedin tanceforintermediatesThiseffectalsoleadstohighercatalyticperthe high concentration of *CO on low-coordination Ag–Cl state for formance due to the electronic perturbation at both sides of the CER25.</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>However, only few studies provide insight on the priority of interface (Fig. 1B)26.</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3210,19 +5400,47 @@
           <t>S0379</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="D80" t="n">
+        <v>3</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Both ofthemexhibit (EDS)mappinganalysisshowsthepresenceofresidualchlorinewitha 3 strong adsorption on the surface of Cu /Cu O model.</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
         <is>
           <t>The *CH CO contentof1.14at%andahomogeneousdistributionamongCu,Cl,and L 2 2 molecular,withtheC(2)endofH C(1)C(2)Opossessingahighpositive O(Fig.2C,SupplementaryFig.10DandSupplementaryTableS2).The 2 charge,servesasakeyintermediatefortheC –Ccouplingreaction, enhancedrectifyinginterfacesoflow-coordinatedCu /Cu Oresultin 2 L 2 suggesting the C –C coupling as a nucleophilic addition reaction anincreasedabsorptionedgeintheultraviolet–visible(UV–vis)diffuse 2 process in the mixed-valence boundary region33.</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Thus, the lowreflectancespectrumacrosstheentirewavelengthrange(insertedin coordinatedCu /Cu OMott–SchottkycatalysthasanenhancedaffiFig.2D).BasedontheKubelka−Munkfunction,theopticalbandgapof L 2 nityforintermediatescomparedtopureCu /Cu O. asemiconductorcanbeextrapolatedfromtheTaucplot(thecurveof P 2 NatureCommunications|( 2024)1 5:5172 3</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3244,19 +5462,43 @@
           <t>S0380</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="D81" t="n">
+        <v>3</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>The *CH CO contentof1.14at%andahomogeneousdistributionamongCu,Cl,and L 2 2 molecular,withtheC(2)endofH C(1)C(2)Opossessingahighpositive O(Fig.2C,SupplementaryFig.10DandSupplementaryTableS2).The 2 charge,servesasakeyintermediatefortheC –Ccouplingreaction, enhancedrectifyinginterfacesoflow-coordinatedCu /Cu Oresultin 2 L 2 suggesting the C –C coupling as a nucleophilic addition reaction anincreasedabsorptionedgeintheultraviolet–visible(UV–vis)diffuse 2 process in the mixed-valence boundary region33.</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
         <is>
           <t>Thus, the lowreflectancespectrumacrosstheentirewavelengthrange(insertedin coordinatedCu /Cu OMott–SchottkycatalysthasanenhancedaffiFig.2D).BasedontheKubelka−Munkfunction,theopticalbandgapof L 2 nityforintermediatescomparedtopureCu /Cu O. asemiconductorcanbeextrapolatedfromtheTaucplot(thecurveof P 2 NatureCommunications|( 2024)1 5:5172 3</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>uncertain</t>
-        </is>
-      </c>
+      <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3278,19 +5520,47 @@
           <t>S0381</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="D82" t="n">
+        <v>4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Article https://doi.org/10.1038/s41467-024-49247-4 converted(αhν)1/nversushνfromtheUV-visspectrum,whereα,h,and electron-richstatusofoxygen-deficientCu+.However,theCu /Cu O P 2 νaretheabsorptioncoefficient,Planckconstant,andfrequencyofthe exhibitsaperfectMott−Schottkystructurewithoutanysignsofdefiphoton,respectively,andnis1/2foradirectbandgapsemiconductor cient oxygen (Fig. 3B and Supplementary Fig. 15).</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
         <is>
           <t>From the Cl 2p or2foranindirectbandgapsemiconductor)33.TheTaucplotexhibitsa spectrums in Fig. 3C, the bonding energy of Cu–Cl also shifts to a well-matchedlinearfitwithn=1/2,whichisinlinewithpreviousartihigherstatewithdeeperAr+etchingduetothepresenceofsufficient cles supporting Cu O as a direct bandgap semiconductor (SuppleClandOatomsinthedepthofCu /Cu O.Thecleanrectifyinginterface 2 L 2 mentaryFig.11)36.TheE valueofCu /Cu Oiscalculatedtobe1.73eV regions of Cu /Cu O ensure smooth absorption and desorption, as g L 2 L 2 by measuring the x-axis intercept of an extrapolated line from the well as the coupling behavior of oxyhydrocarbon intermediates.</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>In linear regime of the curve, which is smaller than that of Cu /Cu O contrastwithCu2pspectraoftheCu /Cu Ospecies,theCu2p3/2 P 2 P 2 (1.85eV).</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3312,19 +5582,47 @@
           <t>S0382</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="D83" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>While the close mechanistic relation between CO and C H was 2 4 thereby confirmed, the DEMS data help uncover an unexpected mechanistic link between CH and ethanol.</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
         <is>
           <t>We demonstrate evidence that adsorbed methyl species, *CH , serve as 4 3 commonintermediatesofbothCH HandCH CH OHandpossiblyofotherCH -Rproducts 3 3 2 3 via a previously overlooked pathway at (110) steps adjacent to (100) terraces at larger overpotentials.</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Our mechanistic conclusions challenge and refine our current mechanistic understanding of the CO electrolysis on Cu catalysts. 2 1DepartmentofChemistry,ChemicalEngineeringDivision,TechnicalUniversityBerlin,Straßedes17.June124,10623Berlin,Germany.2Departmentof Physics,FreeUniversityofBerlin,Arnimallee14,14195Berlin,Germany.3EuropeanSynchrotronRadiationFacility(ESRF),38000Grenoble,France. 4DepartmentofChemistry,UniversityofCopenhagen,Copenhagen2100,Denmark. ✉ email:pstrasser@tu-berlin.de NATURECOMMUNICATIONS| (2021) 12:794 |https://doi.org/10.1038/s41467-021-20961-7|www.nature.com/naturecommunications 1 ;,:)(0987654321</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3346,19 +5644,47 @@
           <t>S0383</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="D84" t="n">
+        <v>2</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>We report a facile one-step pathways11,12, and a reliable device performance at industrial synthesis of 2D CuO NS and then track their unique catalytic conditions13–16.</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
         <is>
           <t>Among a wide variety of catalysts tested for reactivity and concomitant morphological evolution under electrochemical CO reduction reaction (CO2RR), copper-based applied electrode potentials using in situ electrochemical liquid 2 materials, in particular Cu oxides, CuO , have been enjoying TEM and operando X-ray absorption spectroscopy (XAS).</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Next, x attentionthankstotheirwidechemicalselectivityforavarietyof using a new differential electrochemical mass spectrometry multi-carbon products, such as C 2+ hydrocarbons and oxyge- (DEMS) technique with millisecond resolution, we discuss prenates.Ithasbeenreportedthatover16kinds17ofproductscanbe viouslyunreportedtimeevolutionsofkineticonsetpotentialsofa formed on copper catalysts through multiple proton-coupled rangeofdifferentproductsoverthecourseofhours.Conclusions electron transfer processes. from our DEMS data challenge and refine our current mechanThe cathodic electrode potentials during the catalytic CO2RR istic understanding of the mechanistic link between CH and 4 invariably drive the chemical transformation of operating CuO ethanol (EtOH).</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3380,19 +5706,47 @@
           <t>S0384</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D85" t="n">
+        <v>9</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Counter to our revealed only negligible FE drops over 20h.</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
         <is>
           <t>Consistent with currentmechanisticunderstanding,thispointstotheexistenceof C2H4 in situ TEM data, agglomeration resulted in long-term dendritic a common mechanistic intermediate, likely *CH , feeding into 3 morphologies (Supplementary Figs.</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>S27 and S28).</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3414,19 +5768,47 @@
           <t>S0385</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="D86" t="n">
+        <v>2</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>The electron buildingnanostructures19–21,ordesigningsingleactivesites22–25. diffraction pattern of Cu/N C revealed it was amorphous 0.14 Despitetremendous efforthasbeen paid,furtheradvancesare material in Supplementary Fig. 4.</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
         <is>
           <t>To further study the electronic still needed to understand the structure-activity relationship structure of the catalysis, Cu K-edge X-ray absorption spectro- (SAR) and efficient conversion CO to multi-carbon products scopy, X-ray photoelectron spectroscopy (XPS) and soft-X-ray 2 especially for high economy asymmetric C 2+ products (e.g., absorption spectroscopy (XAS) were carried out as shown in ethanol).</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Therefore, the design of catalysts that selectively proFig.1e–gandiandSupplementaryFig.5.TheCu2p XPSfitting 3/2 duceethanol viaelectrochemical CO RRwere supposed tofocus curves revealed that Cu was mainly +1 and +2 valence in Cu/ 2 onminimizingthreecompetingreactionpathwayswhichreduced N C26,27.</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3448,19 +5830,47 @@
           <t>S0386</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="D87" t="n">
+        <v>4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>No C 2+ products are formed at this stage in Fig. 2c. ofCO RRcatalystunderoperandoconditionsiscrucialtoreveal Once applying the potential of −0.8V vs.</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
         <is>
           <t>RHE, the intensity of 2 theintrinsicreactivemechanism.Inordertoidentifytherealistic the scattering peak extremely descended with an additional peak catalytic centers of Cu/N C, operando XAS study were at~2.4Å.ThisisatypicalscatteringfeatureoftheCu–Cubond. 0.14 employed to directly monitor its catalytic behavior.</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>We first The conversion of CO -to-ethanol reaction occurred con2 collectedex-situXASdataofthefullyactivatedCu/N C.When currently.</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3482,19 +5892,47 @@
           <t>S0387</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="D88" t="n">
+        <v>8</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>RHE in Supplementary Fig. 28a.</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
         <is>
           <t>For (−0.699V), implied that the Cu –CuN observed by operando 2 3 comparison, we built a model of Cu –CuN cluster in SuppleXAS is the real active site for reduction of CO to ethanol, as 3 3 2 mentaryFig.28bthatrepresentforthegrowthofCuclustersand shown in Supplementary Fig. 30.</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Furthermore, there were maybetheactivesiteforthemorenegativeappliedpotential.The relatively high energy barriers for State 8→9 (−0.501eV) and calculated average partial charge of three copper atoms in the State11→12(−0.467eV) inthereactionprocessofCu –CuN , 2 3 Cu -CuN cluster was +0.20 e − because of the charge transfer both of which containing –CH and easy to be detected in 2 3 3 betweentheclusterandN-dopedcarbonnanosheets.Thecharge accordance with our FTIR results. exchange primarily occurred with the Cu atom bonding with N The hydrogen evolution reaction is a competing reaction with atoms.</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3516,19 +5954,47 @@
           <t>S0388</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="D89" t="n">
+        <v>8</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>For (−0.699V), implied that the Cu –CuN observed by operando 2 3 comparison, we built a model of Cu –CuN cluster in SuppleXAS is the real active site for reduction of CO to ethanol, as 3 3 2 mentaryFig.28bthatrepresentforthegrowthofCuclustersand shown in Supplementary Fig. 30.</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
         <is>
           <t>Furthermore, there were maybetheactivesiteforthemorenegativeappliedpotential.The relatively high energy barriers for State 8→9 (−0.501eV) and calculated average partial charge of three copper atoms in the State11→12(−0.467eV) inthereactionprocessofCu –CuN , 2 3 Cu -CuN cluster was +0.20 e − because of the charge transfer both of which containing –CH and easy to be detected in 2 3 3 betweentheclusterandN-dopedcarbonnanosheets.Thecharge accordance with our FTIR results. exchange primarily occurred with the Cu atom bonding with N The hydrogen evolution reaction is a competing reaction with atoms.</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>The other two Cu atoms changed slightly before the CO RR53,54.</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3550,19 +6016,43 @@
           <t>S0389</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="D90" t="n">
+        <v>7</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>C 3% HO (or * COH) following the Ag thatissignificantlygreatercomp 2 ar 5 edwiththatfordCu 2 O 2.3% 2 * CO protonationstep.Notably,adsorbed * CHOintermediate and dCu O/Au .</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
         <is>
           <t>This finding evidences that the key bridge 2 2.3% * was observed on dCu O/Ag from ATR-FTIR spectra, and OC H intermediates for EtOH production are more stable on 2 2.3% 2 5 NATURECOMMUNICATIONS| (2022) 13:3754 |https://doi.org/10.1038/s41467-022-31427-9|www.nature.com/naturecommunications 7</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>uncertain</t>
-        </is>
-      </c>
+      <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3584,19 +6074,43 @@
           <t>S0390</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="D91" t="n">
+        <v>8</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>V (with an 85 % iR correction).</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
         <is>
           <t>In situ ATR–IRAS spectroAccordingly, based on the ATR–IRAS spectra analysis, the sc R o H p E y confirmed that boosted EtOH selectivity results from mechanism for boosted EtOH on dCu 2 O/Ag 2.3% can be soundly moderate coordinated surface and optimal oxidation state of the 8 NATURECOMMUNICATIONS| (2022) 13:3754 |https://doi.org/10.1038/s41467-022-31427-9|www.nature.com/naturecommunications</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>uncertain</t>
-        </is>
-      </c>
+      <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3618,19 +6132,47 @@
           <t>S0391</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="D92" t="n">
+        <v>10</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>W.L. performed the HADDF-STEM measurement.</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
         <is>
           <t>X.M. and J.L. carried out the DFT modeling and analyzed the mechanism.</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Q.M. performed the kinetics simulation.</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3652,19 +6194,47 @@
           <t>S0392</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="D93" t="n">
+        <v>7</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Thus, there are two possible pathways for CO reduction, one of which produces CO and the other produces ethanol.</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
         <is>
           <t>Free energy 2 pathways for competing C1 and C2 products were systematically calculated as shown in Extended data Figs. 56–57 and Extended data Table 18.</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>In the case of species 2, the O2SnO…C linkage is cleaved and a face-to-face cyclo-addition between Sn = O double bond and O = CO double bond leads to the CO 2 activation, with a CO adsorption free energy of -0.75 eV.</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3686,19 +6256,47 @@
           <t>S0393</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
+      <c r="D94" t="n">
+        <v>7</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Following the drastic reduction of 1 all carbonyl groups in 4, intermediate 5 is formed as the precursor for C-C coupling.</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
         <is>
           <t>The free energy barrier to C-C bond formation is 0.13 eV, which is much lower than those of Cu-based catalysts (&gt; 1.0 eV) 13,28.</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Thus, intermediate 6, which contains a Sn-C-C-O quaternary ring, is obtained.</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3720,19 +6318,47 @@
           <t>S0394</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
+      <c r="D95" t="n">
+        <v>6</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Article https://doi.org/10.1038/s41467-023-36411-5 Fig.4|StructuralcharacterizationofCu(OD)0.8Ag0.2catalystafterCOreducthecorrespondingatomicallyresolvedEDSmappingofCuandAgattheselected tionreaction.aTEMimageofCu(OD) Ag catalystcross-sectioncutbyFIB. interfacearea.TheatomicratiobetweenCuandAgattheinterface(i.e.,thearea 0.8 0.2 bElectrondiffractionpatternofCu(OD) Ag catalystshownina.cHAADF-STEM withinthegreenbox)wasdeterminedtobe1.12:1. 0.8 0.2 imageandcorrespondingEDSmappingofCuandAg.dHAADF-STEMimageand astheCObindingstrengthissignificantlyloweronAgthanonCu30,54. interfacial sites with relative weak CO adsorption energies on all Thus,itisreasonabletodeducethattwotypesofCusitesarepresent sampleswithdifferentelementratioandballmillingtime. on Cu(OD) 1−x Ag x catalysts, i.e., native Cu(OD) sites, and weak CO Enhanced formation of C 2+ liquid products on Cu(OD) 1−x Ag x adsorption sites consist of Cu atoms located at the interface of could be attributed to the lower C and OH affinities of the Cu–Ag immiscible Cu and Ag particles, whose electronic structure is likely interfacialsites,whichhavebeenpredictedtofavoroxygenatesover modified by the neighboring Ag atoms.</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
         <is>
           <t>The weak CO binding sites ethylene30,31.TheRDSforC productformationsontheCusurface 2+ identified by in situ SEIRAS on the Cu(OD) 1−x Ag x , as compared to wassuggestedtobetheCO ad hydrogenationtoCOH ad byourrecent Cu(OD), can be assigned to the Cu–Ag interfacial sites.</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Ag is well electrokinetic study43.</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3754,19 +6380,43 @@
           <t>S0395</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
+      <c r="D96" t="n">
+        <v>6</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>The subsequent C–C coupling process was knowntobeaweakCObindingmetal,sothefactthatCu–Aginterproposed to occur between COH and CO forming HOCCO 43. ad ad ad facialsitesbindlessstronglythannativeCu(OD)sitesshouldnotcome InvestigationsbasedontheoreticalcalculationreportedthatHOCCO ad asasurprise.Further,theCuandAgdomainsinCu(OD) 1−x Ag x catalysts was favored to go through a hydro-dehydroxylation path forming aretensofnanometersinsize,suggestingthattheinterfacialareais CHCO withthehydrogenationofα-C30,31.Thefurtherhydrogenation ad relativelyminorascomparedtothatofCudomains.Thisexplainsthe of CHCO was shown to form ethylene if either C atom is hydroad relativeconstantspecificethyleneproductionrateuponintroducing genated and to form oxygenates if the O is hydrogenated Ag toCu(OD),asthe CORR activity on Cu domains remainslargely respectively31.</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
         <is>
           <t>While the C affinity of the surface could be used to unchanged(SupplementaryFig.7b).Itfollowsthattheenhancedrates predict the selectivity between oxygenates and ethylene, calculated andselectivitiesforC liquidproductsarecorrelatedwiththeCu–Ag surfacesfavoringoxygenatestendtohavebothlowCandOaffinities. 2+ NatureCommunications|( 2023)1 4:698 6</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>uncertain</t>
-        </is>
-      </c>
+      <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -3788,19 +6438,47 @@
           <t>S0396</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
+      <c r="D97" t="n">
+        <v>1</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Article https://doi.org/10.1038/s41467-023-39351-2 Tunable CO electroreduction to ethanol and 2 ethylene with controllable interfacial wettability Received:21November2022 YanLin1,2,3,5,TuoWang 1,2,3,4,5,LiliZhang1,2,3,GongZhang 1,2,3,LuluLi1,2,3, QingfengChang1,2,3,ZifanPang1,2,3,HuiGao1,2,3,KaiHuang1,2,4, Accepted:8June2023 PengZhang 1,2,3,4,Zhi-JianZhao 1,2,3,ChunleiPei1,2,3&amp;JinlongGong 1,2,3 Checkforupdates ThemechanismofhowinterfacialwettabilityimpactstheCO electroreduc2 tionpathwaystoethyleneandethanolremainsunclear.Thispaperdescribes thedesignandrealizationofcontrollableequilibriumofkinetic-controlled*CO and*Hviamodifyingalkanethiolswithdifferentalkylchainlengthstorevealits contributiontoethyleneandethanolpathways.CharacterizationandsimulationrevealthatthemasstransportofCO andH Oisrelatedwithinterfacial 2 2 wettability,whichmayresultinthevariationofkinetic-controlled*COand*H ratio,whichaffectsethyleneandethanolpathways.Throughmodulatingthe hydrophilicinterfacetosuperhydrophobicinterface,thereactionlimitation shiftsfrominsufficientsupplyofkinetic-controlled*COtothatof*H.The ethanoltoethyleneratiocanbecontinuouslytailoredinawiderangefrom0.9 to1.92,withremarkableFaradaicefficienciestowardethanolandmulti-carbon (C )productsupto53.7%and86.1%,respectively.AC Faradaicefficiencyof 2+ 2+ 80.3%canbeachievedwithahighC partialcurrentdensityof321mAcm−2, 2+ whichisamongthehighestselectivityatsuchcurrentdensities.</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
         <is>
           <t>The electrochemical conversion of carbon dioxide (CO ) into Astheonlymetalwithanegativeadsorptionenergyfor*CObuta 2 value-addedmulti-carbon(C )productsisanattractiverouteto positive adsorption energy for *H, copper (Cu) presents a unique 2+ closethecarbonloop1,2.However,theformationofC products abilitytoproduceC products4,9.However,multipleproductshave 2+ 2+ with high selectivity is still meeting great challenges3.</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>*CO beendetectedonCusurfacesresultinginpoorproductselectivityfor (* denotes the adsorbed species on the surface) and *H are conCu9,10.Previousinvestigationshavefoundthatthecoverageof*COand sidered to be the key intermediates during producing C *HontheCusurfaceplaysacriticalroleindeterminingtheselectivity 2+ products4.Previously,*COcoveragehasbeenwidelyacceptedas of C products4,11.</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3822,27 +6500,55 @@
           <t>S0397</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
+      <c r="D98" t="n">
+        <v>1</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>The electrochemical conversion of carbon dioxide (CO ) into Astheonlymetalwithanegativeadsorptionenergyfor*CObuta 2 value-addedmulti-carbon(C )productsisanattractiverouteto positive adsorption energy for *H, copper (Cu) presents a unique 2+ closethecarbonloop1,2.However,theformationofC products abilitytoproduceC products4,9.However,multipleproductshave 2+ 2+ with high selectivity is still meeting great challenges3.</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
         <is>
           <t>*CO beendetectedonCusurfacesresultinginpoorproductselectivityfor (* denotes the adsorbed species on the surface) and *H are conCu9,10.Previousinvestigationshavefoundthatthecoverageof*COand sidered to be the key intermediates during producing C *HontheCusurfaceplaysacriticalroleindeterminingtheselectivity 2+ products4.Previously,*COcoveragehasbeenwidelyacceptedas of C products4,11.</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Enormous effort has been devoted to catalyst 2+ one crucial factor in the selective produce ethylene5,6.</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
+      <c r="L98" t="inlineStr">
         <is>
           <t>P1:*COCO; P1:COCO</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>uncertain</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3864,19 +6570,47 @@
           <t>S0398</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
+      <c r="D99" t="n">
+        <v>8</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>RHE) of ethylene for CO R, which is 2 2 reductioninelectrolytesatpH1,4,7,andananionexchangemem0.06Vforethylene,andE isthethermodynamicpotential(vs. ethanol brane (AEM, Fumasep FAB-PK-130, Fuel Cell Store) at pH 13.5.</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
         <is>
           <t>The RHE)ofethanolforCO R,whichis0.09Vforethanol39. 2 catholyteofpH1were0.05Msulfuricacid(HSO )and3Mpotassium The C selectivity was calculated as (the rate of C product 2 4 2+ 2+ chloride(KCl)solution,andpHwasadjustedtoaround1byafewdrops formation (R ))/(the rate of total product formation (R )), as product tot of5Mpotassiumhydroxide(KOH).ThecatholyteofpH4were3MKCl follows: solution,andpHwasadjustedtoaround4byafewdropsofH SO . 2 4 ThecatholyteofpH7were3MKClsolution,andpHwasadjustedto C 2+ selectivity=ð2R ethylene +2R acetate +2R ethanol +3R n(cid:3)propanol Þ= around7byafewdropsof1MKOH.ThecatholyteofpH13.5were ðR +R +R +2R +2R ð7Þ CO formate methane ethylene acetate 0.75MKOHsolution.TheanolyteofpH1and4were0.5MH SO ,the anolyte of pH 7 were 1M KHCO , and the anolyte of pH 1 2 3.5 4 were +2R ethanol +3R n(cid:3)propanol Þ×100%, 3 0.75M KOH.</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Electrochemical impedance spectroscopy (EIS) was measuredtoestimatetheelectrolyteresistanceforiRcompensation.</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3898,19 +6632,47 @@
           <t>S0399</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
+      <c r="D100" t="n">
+        <v>10</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>P. et al.</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
         <is>
           <t>The role of glyoxal as an intermediate in the The DFT datasets generated during the current study are available in electrochemical CO reduction reaction on copper.</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>J.</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3932,19 +6694,47 @@
           <t>S0400</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
+      <c r="D101" t="n">
+        <v>10</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Hori, Y., Koga, O., Yamazaki, H. &amp; Matsuo, T.</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
         <is>
           <t>Infrared spectroscopy ACS Catal. 8, 10012–10020 (2018). of adsorbed CO and intermediate species in electrochemical 29.</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Ruiter De, J. et al.</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3966,19 +6756,47 @@
           <t>S0401</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
+      <c r="D102" t="n">
+        <v>10</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>A.</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
         <is>
           <t>A SERS study of SO–4Cl− ion 2 mechanism for electrochemical CO reduction on CuO adsorption at a copper electrode in situ.</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>J.</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4000,19 +6818,47 @@
           <t>S0402</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
+      <c r="D103" t="n">
+        <v>11</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Correlating CO coverage measurements.</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
         <is>
           <t>M.H. performed the in situ SERS measurements of and CO electroreduction on Cu via high-pressure in situ glyoxal and ethanol reduction.</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>F.D. carried out the density functional spectroscopic and reactivity investigations.</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4034,19 +6880,47 @@
           <t>S0403</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
+      <c r="D104" t="n">
+        <v>8</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Along the acetate/ethanol route, OCCH can The crystal structure of the catalysts was studied using XRD with a 2 2 desorb and react in solution with OH− to form acetate21.</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
         <is>
           <t>Following the Bruker-AXS D8 Advance in parallel beam configuration equipped with C route, when highly strained distorted sites are present, an alternative a Cu X-ray tube, a Goebel mirror and equatorial Soller slit (0.3°) as well 2 reaction pathway opens, that is, enabling the reduction of *OCCH to as an energy-dispersive LynxEye detector.</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>The diffraction pattern was 2 *OCHCH by strongly binding the terminal oxygen in a monodentate recorded through the grazing incidence mode with an incidence angle 2 configuration.</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4068,19 +6942,47 @@
           <t>S0404</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
+      <c r="D105" t="n">
+        <v>8</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>However, defects characterized by conditions at the surface of the catalyst. 2+ a highly compressed and distorted coordination environment and deep s-band states are instead generated at higher overpotentials and CORR testing 2 stabilize the adsorption of OCHCH via the terminal oxygen, opening Electrocatalytic measurements were performed with a Biologic SP-240 2 an alternative selective route towards ethanol on copper.</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
         <is>
           <t>By combining potentiostat in an H-type cell equipped with an anion exchange memthe potential-dependent evolution of CO adsorption and C–C coupling brane (Selemion AMV, AGC).</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>The three-electrode system consisted intermediates, we here describe an updated CORR-to-C reaction of the Cu foil as the working electrode, a platinum gauze (MaTecK, 2 2+ scheme that correlates between active sites, surface intermediates and 3,600 mesh cm−2) as the counter electrode and a leak-free Ag/AgCl refproducts.</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4102,19 +7004,47 @@
           <t>S0405</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
+      <c r="D106" t="n">
+        <v>10</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Zhong,M.etal.AccelerateddiscoveryofCO electrocatalysts 2 and the projector augmented-wave method was carried out to usingactivemachinelearning.Nature581,178–183(2020). describetheion-electroninteractions68,69.ACu(111)(4×4)supercell 11.</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
         <is>
           <t>Yang,Y.etal.OperandostudiesrevealactiveCunanograinsfor withalatticeconstantof10.22Å(α=β=90°,γ=120°)wasemployed CO electroreduction.Nature614,262–269(2023). 2 toanchortheAgatomsorsupporttheAg nanoclusters.TheBrillouin 12.</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Kim,Y.etal.Time-resolvedobservationofC–Ccouplinginter13 zonewassampledby3×3×1k-pointsbymeansofMonkhorst-Pack mediatesonCuelectrodesforselectiveelectrochemicalCO 2 scheme with the cutoff of 400eV during the structural relaxation, reduction.Energ.Environ.Sci.13,4301–4311(2020). while 5×5×1 k-points for electronic structure calculation such as 13.</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4136,19 +7066,47 @@
           <t>S0406</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
+      <c r="D107" t="n">
+        <v>10</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Yang,Y.etal.OperandostudiesrevealactiveCunanograinsfor withalatticeconstantof10.22Å(α=β=90°,γ=120°)wasemployed CO electroreduction.Nature614,262–269(2023). 2 toanchortheAgatomsorsupporttheAg nanoclusters.TheBrillouin 12.</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
         <is>
           <t>Kim,Y.etal.Time-resolvedobservationofC–Ccouplinginter13 zonewassampledby3×3×1k-pointsbymeansofMonkhorst-Pack mediatesonCuelectrodesforselectiveelectrochemicalCO 2 scheme with the cutoff of 400eV during the structural relaxation, reduction.Energ.Environ.Sci.13,4301–4311(2020). while 5×5×1 k-points for electronic structure calculation such as 13.</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Zhang,J.etal.AcceleratingelectrochemicalCO reductionto 2 projecteddensityofstates(PDOS)andchargedensitydifference.The multi-carbonproductsviaasymmetricintermediatebindingat convergence criteria for energy and force were set as 10−5eV and confinednanointerfaces.Nat.Commun.14,1298(2023). 0.01eVÅ−1,respectively.Alongtheperpendiculardirection,avacuum 14.</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4170,19 +7128,47 @@
           <t>S0407</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr">
+      <c r="D108" t="n">
+        <v>10</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Zhang,J.etal.AcceleratingelectrochemicalCO reductionto 2 projecteddensityofstates(PDOS)andchargedensitydifference.The multi-carbonproductsviaasymmetricintermediatebindingat convergence criteria for energy and force were set as 10−5eV and confinednanointerfaces.Nat.Commun.14,1298(2023). 0.01eVÅ−1,respectively.Alongtheperpendiculardirection,avacuum 14.</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
         <is>
           <t>Hu,J.etal.Edge-richmolybdenumdisulfidetailorscarbon-chain space at least 18Å was added to eliminate the effects of periodic growthforselectivehydrogenationofcarbonmonoxidetohigher structure, and the dispersion corrected density functional theory alcohols.Nat.Commun.14,6860(2023).</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>(DFT-D3) was utilized to include van der Waals (vdWs) interaction 15.</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4204,19 +7190,47 @@
           <t>S0408</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
+      <c r="D109" t="n">
+        <v>11</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Zhao,Y.etal.ElucidatingelectrochemicalCO reductionreaction 2 2 productsinacidicmedia.Nat.Catal.5,564–570(2022). processesonCu(hkl)single-crystalsurfacesbyinsituRaman 32.</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
         <is>
           <t>Wang,X.etal.EfficientelectricallypoweredCO -to-ethanolvia spectroscopy.Energ.Environ.Sci.15,3968–3977(2022). 2 suppressionofdeoxygenation.Nat.Energy5,478–486(2020). 55.</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Zhan,C.etal.RevealingtheCOCoverage-DrivenC-CCoupling 33.</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4238,19 +7252,47 @@
           <t>S0409</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
+      <c r="D110" t="n">
+        <v>16</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>At a cell voltage of -3.47 V, Co -Sub-CuS catalystsS achieved a FE of 78.7%, a 0.050 EtOH S partial current density of ≈ 550.9 mA cm-2 for EtOH, and aE full-cell energy efficiency (EE ) full‑cell R of ≈ 26.1% for EtOH (Supplementary Fig. 53), compaPred with previously reported electrocatalysts N for selective ethanol production in an MEA electrolyzer, exhibited competitive electrocatalytic I E performance (Supplementary Table 10).</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
         <is>
           <t>The FE /FE ratio at different cell voltages was also C2 CO L C evaluated (Supplementary Fig. 54), with a ratio of ≈ 13 at -3.47 V, indicating the high C-C coupling I T orientation capability.</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>TheR CO 2 ER stability of Co 0.050 -Sub-CuS catalysts in MEA electrolyzers was A systematically evaluated (Fig. 2l), showing well stability for 305 h at a total current density of 700 mA cm-2, with a stable cell voltage ranging from -3.45 V to -3.72 V, and an average FE of ≈ EtOH 76%.</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4272,19 +7314,47 @@
           <t>S0410</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr">
+      <c r="D111" t="n">
+        <v>18</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>(e) The calculated infrared-active vibrational frequency of *OCCOH on Co -Sub-CuS.</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
         <is>
           <t>(f) The calculated infrared-active vibrational 0.050 frequency of *CHCHO* on Co -Sub-CuS, the right is the different adsorption modes of two key 0.050 intermediates *CHCHO* and *CHC*OH at dual-Cu sites.</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>(g) In-situ Raman peaks on Co -Sub0.050 CuS in 1 M KOH from 0.1 V vs.</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4306,27 +7376,55 @@
           <t>S0411</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr">
+      <c r="D112" t="n">
+        <v>24</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>(b) On the Co-Sub-CuS catalyst, *CO and *COH co-adsorb on Cu sites and asymmetrically couple to form OCCOH*, with dashed arrows denoting Cu-Cu distances.</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
         <is>
           <t>(c) Energy profiles for the *CO + *COH → OCCOH* on VsCuS and Co-Sub-CuS.</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Initial state (IS), transition state (TS) and final state (FS) are depicted in the</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
         <is>
           <t>P1;P3</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr">
+      <c r="L112" t="inlineStr">
         <is>
           <t>P1:OCCO; P3:*COH</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>uncertain</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4348,19 +7446,47 @@
           <t>S0412</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr">
+      <c r="D113" t="n">
+        <v>5</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Theoretically, the latter configuration could efficiently prevent the loss of O atom in subsequent steps, thereby favoring the formation of C 2 oxygenates6,8,17,19.</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
         <is>
           <t>In contrast, the former configuration often occurs spontaneously due to its low free energy barrier, leading to dehydration during subsequent protonation steps and ultimately producing only C hydrocarbons5,14,17-19.</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>In this regard, the binding strength of O atoms in the 2 *CHCHO* on the surface of Cu-based electrocatalysts could seSrve as a crucial descriptor for S evaluating the bifurcation potential between C H and EEtOH formation.</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4382,19 +7508,47 @@
           <t>S0413</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr">
+      <c r="D114" t="n">
+        <v>5</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Therefore, there is a pressing need L C to develop a rational and versatile catalyst design strategy to direct the branching SDI pathway I T toward EtOH, focusingR on controlling the adsorption configuration of oxygen-binding A intermediates (*CHCHO*).</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
         <is>
           <t>To date, strategies aimed at modifying surface oxophilicity have provided alternative routes to influence the adsorption configuration of oxygen-binding intermediates through techniques such as surface engineering20,21, doping effects22, alloying23,24, and interface engineering25.</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>These approaches fundamentally rely on manipulating the electronic structure of active sites exposed at surface layer to optimize the coordination capacity of oxygen-binding intermediates.</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4416,19 +7570,47 @@
           <t>S0414</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr">
+      <c r="D115" t="n">
+        <v>11</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Pseudopotentials built by the 61,e202114238(2022). projector-augmented wave (PAW) method and Perdew−Burke−Ern16.</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
         <is>
           <t>Bi,J.etal.Constructionof3Dcopper-chitosan-gasdiffusionlayer zerh(PBE)63exchange-correlationfunctionwithintheVanderWaals electrodeforhighlyefficientCO electrolysistoC alcohols.Nat. 2 2+ (vdW)correctionexploitedbyGrimme(DFT+D3)64.Similarcalculated Commun.14,2823(2023). parameters had been performed in Previous works65,66.</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>We con17.</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4450,27 +7632,55 @@
           <t>S0415</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr">
+      <c r="D116" t="n">
+        <v>6</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Upon comparison with recently theelectrodesurface(SupplementaryFig.14a,14b).Duringthekept reported Cu electrocatalysts for C HOH production, the recon2 5 negative potential, the mass of the electrode remained essentially structed CA Cu electrocatalyst exhibited the extraordinary C HOH 2 5 stable,inwhichthecitrate-coordinatedCuchelatewasreconstructed. electrosynthesis in terms of FE and j (Fig. 4f, Supplementary When the applied negative potential subsequently changed to the Table1)15–17,20–36.Inaddition,toexcludethepossibilityofinterference open-circuit potential state, the mass of the citrate-coordinated Cu withtheproductselectivitycausedbytheconvertoftheCAintosome chelate electrode decreased rapidly and more greatly than that of newspeciesunderelectrochemicalconditions,correspondinglyeleccommercial Cu.</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
         <is>
           <t>Also, the mass change over citrate-coordinated Cu trochemicalperformancewasalsotestedoncommercialCuinelecchelatefromnegativepotentialtoopen-circuitpotentialwashigher trolytewith10mMCAandwithoutCO inlet.The1HNMRspectrumof 2 thanthestatefromtheopen-circuittothenegativepotentialapplied. the electrolyte after reaction wascollected and analyzed, where no This demonstrated that from constant negative potential to openliquid products (C HOH, n-propanol, CH COO−, and HCOO−) were 2 5 3 circuit state, in addition to the K+, a small amount of CA also was detected, verifying the CA was stable under electrochemical condidesorbedfromtheinterface.ThisresultalsoreflectedthattheCAcan tions(SupplementaryFig.15). beenrichedintheHelmholtzplanethroughtheinsidetoon-surface Inordertoanalyzeandelucidatetheeffectsofanionsdiffusionby diffusionmodel.Also,themasschangeofcommercialCuelectrodein insidetoon-surfacebehavioronthecations(mainlyK+)diffusion,in1MKOHelectrolytewith1mMCAwassimilartothatinthecaseofthe situ electrochemical impedance spectroscopy (EIS) was adopted to electrolytewithoutCAwhentheappliedpotentialfromopen-circuitto detect the impedance variations during the electrochemical reconnegativecondition(SupplementaryFig.14b,14c).Thissuggestedthat structionandthereleaseofCAfromcitrate-coordinatedCuchelate. themasschangecorrespondingtoCAadsorptionfromtheelectrolyte Whenapplyingaconstantpotential,theresistanceinhigh-frequency waslowcomparedtothatofK+adsorption.AndtheCAwasdifficultto regionintheEISdisplayedagradualincrease.Whenthepotentialwas diffusefromtheelectrolytetotheelectrodesurfaceandenrichedin applied for a period time, the resistance nearly no longer changed theHelmholtzplane,i.e.,thediffusionmodefromoutsidetoabove- (Supplementary Fig. 16a).</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr">
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>While at the low-frequency region, the surface,whichmayberestrictedbydiffusivemasstransferresistance relationshipbetweentheZ′(realpart)andw−1/2(w:angularfrequency) andelectrostaticrepulsion.Correspondingly,anundesirablelocalized reflected the impedance of ion diffusion, and a larger slope of the microenvironmentandanunsatisfactoryelectrocatalyticperformance curveafterfitting(σ:Warburgcoefficient)waspresented,indicativeof werepresentedoverCucatalystintheelectrolytewith1mMCA,and thelargeriondiffusionresistance.AsshowninSupplementaryFig.16b, theoverallperformanceofCO RRwasdramaticallyfarinferiorcomthe ion diffusion resistance increased significantly during the 2 paredwiththatofCACucatalyst.Finally,suchauniqueinsidetooninitial stage of electrochemical reconstruction and then remained surfacediffusionapproachderivedfromCA-coordinatedCuchelate stable.</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr">
+      <c r="L116" t="inlineStr">
         <is>
           <t>P5:HCOO</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>uncertain</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4492,19 +7702,47 @@
           <t>S0416</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
+      <c r="D117" t="n">
+        <v>2</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>In this regard, acetate exceeds 170-fold, 55-fold, and 35-fold, respectively.</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
         <is>
           <t>The recent in situ/operando surface-enhanced Raman spectroscopic formation of n-propanol is also observed at −0.75 V with a RHE investigations provided initial evidence of the existence of oxipartial current density of ~0.5mAcm −2 in the presence of O , 2 dizedCuspeciesatreducingpotentials21.Amuchlessdiscussed, while no detectable amount of n-propanol is observed at but arguably more important, aspect is whether the oxidized Cu thispotentialintheoxygen-freeatmosphere.Theonsetpotential species, if they indeed exist at the CO RR conditions, contribute of n-propanol in the oxygen-free atmosphere occurs at as 2 to enhanced reactivity of Cu-based catalysts after oxidative negative as −0.90 V (Fig. 1d), and to achieve a similar rate RHE treatments.</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr"/>
-      <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>It is conceivable that Cu oxide and/or hydroxide of ~0.5mAcm −2 requires an additional 250mV overpotential, species are mere spectators during the CO RR, while prei.e.,−1.00V (Fig.1f).UnlikeC products,theformationrate 2 RHE 2 ferentially exposed facets or defects, e.g., located at the grain ofn-propanoldoesnotshowadrasticfurtherenhancementasthe boundarieson themetallic Cusurface, induced by thetreatment O ratio increases from 10 to 20%, suggesting its distinct 2 are the real cause of change in the catalytic performance22–25. chemistry in forming an additional carbon bond after their This has been shown in our recent work in the CO-reduction common rate-determining step of C–C coupling between two reactiononCu26.Thus,establishingadirectcorrelationbetween adsorbed CO molecules29,31,32.</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4526,19 +7764,43 @@
           <t>S0417</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr">
+      <c r="D118" t="n">
+        <v>5</v>
+      </c>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr">
         <is>
           <t>100 estimated via density functional theory calculations.</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr"/>
-      <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>The free experiments showing that polycrystalline Cu leads to a product energy profiles of the rate-determining steps (RDS) in the fordistribution similar to that on Cu(100)48.</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4560,19 +7822,47 @@
           <t>S0418</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr">
+      <c r="D119" t="n">
+        <v>2</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>The electrolytes werecirculated inboth compartments by adual-channel between the pulsed CO 2 RR parameters and the observed peristaltic pump (FAUST PLP380) at a constant flow controlled by selectivity trends. the pump’s rotation speed, which was set to 10 rpm.</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
         <is>
           <t>The Previous studies of the pulsed CO 2 RR in H-type cells have electrochemical experiments were performed using a potentiostat reported that oxidative potentials are beneficial for hydro- (AutolabPGSTAT302N).TheOhmicresistancewasdeterminedby carbon and alcohol production.21,23 Here we extend such electrochemical impedance spectroscopy (EIS).</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>The potential values studies to a flow cell configuration and high current densities, after iR compensation were converted to the reversible hydrogen using highly active shape-selected Cu O nanocube (Cu NC) electrode(RHE)referencescaleusingE(vsRHE)=E(vsAg/AgCl)+ catalysts.</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4594,19 +7884,47 @@
           <t>S0419</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr">
+      <c r="D120" t="n">
+        <v>2</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Cu NCs were OperandoXASmeasurementswereperformedattheP64beamline prepared by modifying a previously reported procedure.32,33 In a of thePETRA-IIIsynchrotron(Hamburg,Germany).Time-resolved typical synthesis, a dilute alkaline solution containing Cu ions was quickX-rayabsorptionfinestructure(QXAFS)spectrawerecollected prepared by adding 8 mL of a CuSO·6HO solution (0.1 M) and influorescencemode.Ahomemadeflowcellwasusedtoacquirethe 4 2 28 mL of a NaOH solution (1 M) to 732 mL of ultrapure water at XASspectraunderthereactionconditions.Intheoperandoflowcell,a roomtemperature.Afterthemixturewasstirredfor10s,32mLofan KaptonwindowwasinstalledtoallowX-raystoilluminatethecatalyst L-ascorbicacidsolution (0.25M)was added.The solutionwas then on the GDE from the back and collect the emitted fluorescence stirredforafurther13min.Thesolutionwascentrifugedandwashed (Figure S2).</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
         <is>
           <t>All samples were measured in air and under operando severaltimeswith waterand ethanol. conditions corresponding to potentiostatic and pulsed electrolysis.</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>To prepare the electrodes on a GDE, a catalyst ink was made by The details of the XAS data acquisition and processing, as well as dispersing 0.5 mg of the catalyst powder with ∼22 wt % of Nafion schematics of the flow cell employed, are given in Supplementary (relative to the total loading, Sigma-Aldrich) in 1 mL of methanol.</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4628,19 +7946,47 @@
           <t>S0420</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr">
+      <c r="D121" t="n">
+        <v>7</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Journal of the American Chemical Society pubs.acs.org/JACS Article Previous studies in H-type cells have demonstrated that the presenceofdefects,specificfacets,andgrainboundariesonthe Cu surface promotes the C−C coupling required for C product generation.5−8,45−47 It should be noted not only tha 2 t the pulse electrolysis treatment employed here affects the catalyst morphology, chemical state, and local pH around the activemotifsbutalsothattheoxidativepotentialsmightresult intheoxidationofalcohols,aldehyde,andformatetogenerate more carbonaceousintermediates(including *CO), which are keyintermediatestoC products,particularlyC H .However, 2+ 2 4 thelattereffectwasdiscardedasasignificantcontributortothe selectivity trends obtained, since the enhanced C selectivity 2+ was preserved after the pulse treatment was interrupted and the same sample was subsequently measured under potentiostatic conditions (constant negative applied potential).</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
         <is>
           <t>This indicates that irreversible changes in the sample morphology Figure7.(a)Operandosurface-enhancedRamanspectraunderOCP, takingplaceduringthepulsetreatmentaremainlyresponsible potentiostatic operation at −0.7 V, and pulsed conditions with differentE values.DashedlinesrepresenttheRamanbandsofCuO for the improved C 2+ selectivity detected.</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr"/>
-      <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>(black),Cu an −OH(red), andCu−CO(blue). 2 In the case of pulses with E an = 1.2 V, where CH 4 is produced as the main product, XAS and SERS point to the formationofaCu Olayerthatcannotbefullyremovedduring 2 and368cm −1.Thesebandsareassociatedwiththepresenceof the cathodic pulse.</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4662,19 +8008,47 @@
           <t>S0421</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr">
+      <c r="D122" t="n">
+        <v>2</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>The Raman signatures of the different grated efficientlydopethesurface ofCubywithdrawingelectronsfrom molecules were detected on the surface of the Ag–Cu electrodes, the metal surface leading to the formation of Cu δ+ species. while strong FTIR bands at 1303, 1584, and 1622cm −1 are only Compared to pristine non-functionalized and alkylpresented on N SN-, N Nand C N-functionalized Ag–Cu 2 3 2 functionalized electrodes, the modified electrodes display a clear electrodesandattributedtotheC–CorC–Nstretching,theNH 2 improvement of the reaction rates and Faradaic efficiency scissor and the C–N stretching modes respectively45–47 (Suppletowards the production of C 2+ products.</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
         <is>
           <t>Operando Raman and mentaryFig.9).Thesuccessfulfunctionalizationwiththiadiazole X-rayabsorptionspectroscopy(XAS)suggestthatthepresenceof and triazole is further confirmed from the deconvolution of the Cu δ+ with 0 &lt; δ&lt;1—due to the p-doping of the Cu surface— X-ray photoelectron spectra from the S2p and N1s regions favorstheformationofadsorbedCOwiththeatopconformation respectively (Supplementary Figs. 10b, c).</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>The peak of S2p was which is a known key intermediate species involved in the C–C deconvolutedintothreedoubletsat162.75,164.23,and168.31eV coupling step associated with the formation of multicarbon for the S2p , corresponding to S–H and S–C bonds on both 3/2 products.</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4696,19 +8070,47 @@
           <t>S0422</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr">
+      <c r="D123" t="n">
+        <v>2</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Operando Raman and mentaryFig.9).Thesuccessfulfunctionalizationwiththiadiazole X-rayabsorptionspectroscopy(XAS)suggestthatthepresenceof and triazole is further confirmed from the deconvolution of the Cu δ+ with 0 &lt; δ&lt;1—due to the p-doping of the Cu surface— X-ray photoelectron spectra from the S2p and N1s regions favorstheformationofadsorbedCOwiththeatopconformation respectively (Supplementary Figs. 10b, c).</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
         <is>
           <t>The peak of S2p was which is a known key intermediate species involved in the C–C deconvolutedintothreedoubletsat162.75,164.23,and168.31eV coupling step associated with the formation of multicarbon for the S2p , corresponding to S–H and S–C bonds on both 3/2 products.</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>When assembled in a membrane electrode-assembly thiadiazole and triazole, respectively48.</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4730,19 +8132,47 @@
           <t>S0423</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr">
+      <c r="D124" t="n">
+        <v>4</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Compared with pristine and t d a e r m y o F n i s g t . rat 2 e 0 d ). st T ab h l e e p N er 2 f S o N rm - a a n n c d e w N it 3 h Na fu r n et c e t n io t n io a n liz o e f d th e e le c c u tr r o r d en es t alkyl-functionalized electrodes, both N SN and N N functional groupspresentthelargestFE =FE ra 2 tios—illustr 3 atingthatthe densityof94%and91%respectively—sharplyimprovedcompared functionalizationwitharoma C ti 2 c þ hete H ro 2 cyclesefficientlydirectsthe N to N tha fu t n o c f ti p o r n is a t l i i n ze e d A A g g – – C C u u a e t le 7 c 8 tr % o . d T es h r e em FE ain fo s r a C s 2 h + igh of a N s5 2 S 4 N %a an n d d reaction pathway towards the formation of C 2+ products while 46 3 .5% after 20h, which demonstrates that the selectivity for the suppressing the HER.</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
         <is>
           <t>To get a more accurate estimation of the reaction pathway on the surface of the electrode is not modified intrinsic CO 2 RR performance of the functionalized Ag–Cu elecduringelectrolysis.Tofurtherconfirmtheapparentstabilityofthe trodes, we estimated the electrochemically active surface area of functionalized electrode, we performed XPS spectroscopy to Cu(CuECSA)andAg(AgECSA)forthe15at.%Ag–Cuandthe evaluate the N:Cu ratio after 30min, 1h, 24h, and 100h.</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr"/>
-      <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>The N SN-15 at.% Ag–Cu catalysts using Pb underpotential deposi2 ratioisfound tobevirtuallyconstantsuggestinga robustgrafting tion (Pb UPD) (Supplementary Figs. 17, 18 and Supplementary of the functional groups on the catalyst surface (Supplementary Table2).ThepartialcurrentdensitiesforC 2+productsmeasured Figs. 21, 22andSupplementary Table3). in H-cell were normalized by the ECSA values for Cu.</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4764,19 +8194,47 @@
           <t>S0424</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr">
+      <c r="D125" t="n">
+        <v>6</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Similarly, no obvious shift of correlation between the density of adsorbed *CO on the catalyst the Cu K-edge was observed from the in situ XANES surface and the formation of C–C bonds in agreement with the measurements at increasing applied potential up to −1.2V vs.</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
         <is>
           <t>*CO being the key intermediate involved in the dimerization RHE and the spectra virtually overlap.</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>This confirms the reaction and the formation of C 2+ products.</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4798,19 +8256,43 @@
           <t>S0425</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr">
+      <c r="D126" t="n">
+        <v>6</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>To gain insight into the C–C coupling CO 2 RR using a membrane electrode-assembly (MEA) flow mechanismonfunctionalizedandpristineAg–CuduringCO RR, electrolyzer.</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
         <is>
           <t>To evaluate the potential of our approach for 2 the surface of the catalysts was probed using operando Raman practical applications towards the electrosynthesis of C 2+ prospectroscopy in order to elucidate the interactions between the ducts, we integrated the different functionalized bimetallic 6 NATURECOMMUNICATIONS| (2021) 12:7210 |https://doi.org/10.1038/s41467-021-27456-5|www.nature.com/naturecommunications</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr"/>
-      <c r="F126" t="inlineStr"/>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>uncertain</t>
-        </is>
-      </c>
+      <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4832,19 +8314,47 @@
           <t>S0426</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr">
+      <c r="D127" t="n">
+        <v>2</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>This work provides theoretical guidance for the design to, for instance, subsurface oxygen12, grain boundaries10,13, of highly selective Cu-based catalysts and develops a versatile exposed facet14, and local pH15.</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
         <is>
           <t>Moreover, recent study by Ager research framework, machine-learning accelerated theoretical et al.16 showed that different C 2+ products are generated from calculations, coupled with actionable experiments, for analyzing specificactivesites onOD-Cuvia isotopelabeling.</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>However, the atomic structures of active sites in heterogeneous catalytic currentunderstandingofatom-scaleactivesitesoverOD-Cufalls systems. short of expectation, impeding the rational design of catalysts converting CO 2 to specific product, like ethylene and ethanol, Results with high selectivity.</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4866,19 +8376,47 @@
           <t>S0427</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr">
+      <c r="D128" t="n">
+        <v>2</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Therefore, identifying atom-scale product-spe- “oxide-derived” process, the two-step approach was employed. cific active sites for CO R over OD-Cu catalysts remains grand 2 First,NN-MDwasperformedwithcanonicalensemble(NVT)to challenges. obtain a thermodynamically balanced surface structure.</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
         <is>
           <t>SubseThe development of machine-learning-based new calculation quently,theoxygenvacancyformationenergies(E )ofsurfaceO methods is a frontier in the field of theoretical catalysis, at the ov were calculated, wherein O atoms with lower vacancy formation same time, a promising route to analysis the active sites in energies were removed to represent the reduction process, complex heterogeneous catalytic system17,18.</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Goddard and cothereby forming a partially reduced surface.</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4900,19 +8438,43 @@
           <t>S0428</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr">
+      <c r="D129" t="n">
+        <v>2</v>
+      </c>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr">
         <is>
           <t>Keywords: CO reduction reaction, transition metal phosphides, imidazolium, in-situ Raman, 2 ethanol electrosynthesis.</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Highlights • High energy efficiency electrochemical conversion of CO to ethanol enabled by 2 employing MoP nanoparticles covered by an imidazolium-functionalized ionomer (Im). • The Im reduces mass transport limitations of the reaction and fine-tunes the catalytic properties of the surface-active sites.</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4934,19 +8496,43 @@
           <t>S0429</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr">
+      <c r="D130" t="n">
+        <v>20</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Our peak analysis shows that the intensity of the P2 peak for MoP-Im is higher than that of MoP catalyst, and P2/P1 ratio for MoP-Im catalyst at the potential -0.5 V (P2/P1 ≅ 1.47) is about 47% higher than that of MoP catalyst (P2/P1 ≅ 1).</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
         <is>
           <t>The higher P2/P1 ratio for MoP-Im indicates that the *CO intermediates are stabilized on the surface of MoP-Im which results in higher C-C 20 )stinu .bra( ytisnetnI P1 P2 *CO P3 MoP-Im 2 Raman Shift (cm-1) 2_ _ CO 3 E = -0.5 V WE OCP 200 400 600 800 1000 1200 1400 1600 1800 2000 2200 2400 )stinu .bra( ytisnetnI a b P1 P2 *CO P3 MoP 2 Raman Shift (cm-1)</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr"/>
-      <c r="F130" t="inlineStr"/>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>uncertain</t>
-        </is>
-      </c>
+      <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4968,19 +8554,47 @@
           <t>S0430</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr">
+      <c r="D131" t="n">
+        <v>21</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>In-situ Raman spectroscopy confirmed that the imidazolium layer not only increases the number of CO molecules near the catalyst 2 surface but also stabilizes adsorbed *CO – and *CO intermediates at the surface of catalyst that 2 promotes C-C coupling and C H OH formation activity of MoP-Im.</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
         <is>
           <t>Moreover, DFT calculations 2 5 suggest that the Im can increase the CO binding strength and charge transfer to accelerate the 2 reaction.</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr"/>
-      <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>The demonstrated electrocatalytic process using the TMP class of catalysts and imidazolium-based ionomer in this study suggests a promising approach for lowering eCO RR 2 barriers toward high rate C + production in a sustainable fashion. 2 Credit authorship contribution statement 21</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5002,19 +8616,47 @@
           <t>S0431</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
+      <c r="D132" t="n">
+        <v>24</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Dlott, R.I.</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
         <is>
           <t>Masel, In Situ Spectroscopic Examination of a Low Overpotential Pathway for Carbon Dioxide Conversion to Carbon Monoxide, The Journal of Physical Chemistry C. 116 (2012) 15307–15312. https://doi.org/10.1021/jp210542v. [8] D.</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>V Vasilyev, P.J.</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5036,19 +8678,47 @@
           <t>S0432</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr">
+      <c r="D133" t="n">
+        <v>1</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>A challenge for the practical application of complex elecdurations, where a balance between metallic copper and distorted trochemical processes, such as the CO reduction reaction (CORR) copper oxide species on the catalyst surface is achieved, as revealed 2 2 over copper-based catalysts, is control of selectivity1–5.</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
         <is>
           <t>One of the by time-resolved operando X-ray absorption spectroscopy (XAS) critical parameters affecting the catalyst’s properties and function— and high-energy X-ray diffraction (XRD), and supported by quasi its oxidation state6,7—can be conveniently manipulated in situ by in situ X-ray photoelectron spectroscopy (XPS).</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Our study demchoosing appropriate applied potentials.</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5070,19 +8740,47 @@
           <t>S0433</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr">
+      <c r="D134" t="n">
+        <v>3</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>The removal of the electrochemically grown oxide reversible changes in the catalyst structure and composition under species is quick, which contrasts with the sluggish initial reduction pulsed CORR with Δt = Δt = 10 s and E = 0.6 V are evidenced by of the CuO phase under the static CORR.</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
         <is>
           <t>This implies that only 2 a c a 2 2 SENAX )3–Å( SFAXE-TF a b XANES FT-EXAFS Δ-XANES × 100 Δ-FT-EXAFS × 10 R (Å) 2θ (°) ytisnetni DRX-Δ 0 2 4 6 8 t (s) d E(t) I(t) 20 mA w = 0.58 LCA-XANES Cu(0) 0 0.5 0.05 8,980 9,000 9,020 0 2 4 w 0 = 0.38 Cu(I) c 0.05 9.70 9.75 9.80 Cu(311) XRD Relative peak intensity Cu (311) 0.1 CuO 2 (111) CuO 0.5 nm 2 CL = (220) 0 17.3 nm Cu Cu Cu 2 O (311) Coherence length 4 6 8 10 0 100 200 t (s) Fig. 2 | Evolution of the operando Cu K-edge XAS and XRD data under pulsed CORR. a–c, Changes in XANES (a), EXAFS (b) and XRD (c) data under an 2 anodic pulse.</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr"/>
-      <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Data corresponding to different times since the onset of the anodic pulse are shown (see colour bar).</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5104,19 +8802,47 @@
           <t>S0434</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr">
+      <c r="D135" t="n">
+        <v>8</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Alkaline conditions were found to suppress the selectivity maps at varying potentials (Supplementary Fig. 16). kinetically feasible but thermodynamically less favorable pathSimilar maps based on (ΔG CO*, ΔG OH*) have been introduced ways towards C 2 HCs at low overpotential.</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
         <is>
           <t>We have used recentlytodescribeselectivitytowardsvariousC products42.Also, scaling relations of transition state energies of key steps to 1 mapsbasedon(ΔG CO*,ΔG C*)havebeenestablishedtounderstand determine the C 2 Oxy/HC selectivity with two thermodynamic the C /C selectivity, offering additional constraints to the optimal descriptors: the adsorption energy of C* and OH*.</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>We found 2 1 ΔG C* range that allows facile C 2 production from C*35.</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5138,19 +8864,47 @@
           <t>S0435</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr">
+      <c r="D136" t="n">
+        <v>1</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Davis, Carlos Andrés Girón Rodriguez, Andreas Vishart, Wanyu Deng, Qiucheng Xu, Shaofeng Li, Peter Benedek, Junjie Chen, Johanna Schröder, Joseph Perryman, Dong Un Lee, Thomas F.</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
         <is>
           <t>Jaramillo, Ib Chorkendorff, Brian Seger* KEYWORDS. electrochemical CO reduction, operando X-ray measurements, alloy, aldehyde, 2 strain effect, d-band center, oxophilicity.</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr"/>
-      <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>ABSTRACT.</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5172,19 +8926,47 @@
           <t>S0436</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr">
+      <c r="D137" t="n">
+        <v>11</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>As a result, aldehyde would desorb from the catalyst surface before being further reduced to alcohols20,30,44.</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
         <is>
           <t>To gain more insights into the effects of Ag on C-C coupling, Figure 3c looks at the branching point between C-C coupling to C products versus protonation to the C1 product CH .</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr"/>
-      <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>The 2+ 4 promoted C /CH ratio primarily occurs by the suppressed CH formation upon alloying with 2+ 4 4 11</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5206,19 +8988,47 @@
           <t>S0437</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr">
+      <c r="D138" t="n">
+        <v>4</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>improved ethanol production when the Cu/Cu O composite was dispersed with trace amounts of 2 Ag31.</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
         <is>
           <t>The above divergencies demonstrate a yet-to-be-fully-understood mechanism of the interaction between Cu and Ag in eCO2RR, which generally falls into three aspects: i) if Cu and Ag have miscible phases, ii) if there is electronic and/or structural interaction between Cu and Ag, and if so, iii) how is the intermediate adsorption influenced and the resultant variation in selectivity.</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr"/>
-      <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Being able to track the catalysts’ variations in crystallite and coordination environment in the eCO2RR environment can provide more insightful information regarding the above points.</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5240,19 +9050,47 @@
           <t>S0438</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr">
+      <c r="D139" t="n">
+        <v>9</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>In CuAg alloys, CO produced on Ag can also create a high local CO partial pressure at the adjacent Cu sites14,18,20, leading to a CO-enriched local environment, which facilitates the following C-C coupling and thus suppresses direct *CO hydrogenation to produce CH , as shown in Figure 4b and c.</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
         <is>
           <t>Previous DFT calculations also 4 revealed weakened *H binding on the Cu surface as *CO coverage increases32 with experimental results validating this33.</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr"/>
-      <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Considering that Cu is located at the weak binding side of the volcano plot of H evolution, a weaker *H binding energy will further suppress H production34.</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5274,19 +9112,47 @@
           <t>S0439</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr">
+      <c r="D140" t="n">
+        <v>12</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Authorcontributions 2 58.</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
         <is>
           <t>Chen,C.etal.Theinsitustudyofsurfacespeciesandstructuresof G.Z.conceivedandsupervisedthestudy.Y.Z.conductedexperiments oxide-derivedcoppercatalystsforelectrochemicalCO reduction. andanalyzeddata.Y.C.performedandpreparedtheDFTcalculations 2 Chem.Sci.12,5938–5943(2021). section.X.W.andY.F.conductedsomeexperiments.Z.D.andM.C. 59.</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr"/>
-      <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Zhan,C.etal.RevealingtheCOcoverage-drivenC–Ccoupling assistedtheelectrochemicalinsituFourierTransformInfrared(FTIR) mechanismforelectrochemicalCO reductiononCuOnanocubes spectroscopyandRamananalysis.G.Z.contributedsignificantlytothe 2 2 viaoperandoRamanspectroscopy.ACSCatal.11,7694–7701(2021). analysisandmanuscriptpreparation.Allauthorsparticipatedinthe 60.</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5308,19 +9174,47 @@
           <t>S0440</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr">
+      <c r="D141" t="n">
+        <v>1</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Millisecond-resolved differential electrochemical mass spectrometry (DEMS) track a previously unavailable set of product onset potentials.</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
         <is>
           <t>While the close mechanistic relation between CO and C H was 2 4 thereby confirmed, the DEMS data help uncover an unexpected mechanistic link between CH and ethanol.</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr"/>
-      <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>We demonstrate evidence that adsorbed methyl species, *CH , serve as 4 3 commonintermediatesofbothCH HandCH CH OHandpossiblyofotherCH -Rproducts 3 3 2 3 via a previously overlooked pathway at (110) steps adjacent to (100) terraces at larger overpotentials.</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5342,19 +9236,47 @@
           <t>S0441</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr">
+      <c r="D142" t="n">
+        <v>6</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>We conclude that facet-orientated CuO NS rapidly associatedwithundercoordinatedCuatoms.Thisisinagreement transformintonanoscalereactivesheetfragmentsthatslowlyrewith the in situ TEM results that suggested the formation of assemble into stable large agglomerations and tree-like Cu nano-sized Cu sheet fragments.</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
         <is>
           <t>Undercoordinated Cu sites dendrites at rates depending on applied potential/reaction time. formed during the CuO NS fragmentation and visualized in Dendritic structures are known to emerge in diffusion-limited Fig. 3, typically exhibit strong chemisorption that has been growth regimes48,49, typically present under convective flow associated with outstanding C-C coupling23,25. conditionsofelectrochemicalflowcells.Wethereforehypothesize dendritic structures—characterized by their unique tree-like MechanisticimplicationsfromDEMS-basedcatalyticratesand arborization with self-similar branch structure across several product onset potentials.</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>A differential electrochemical mass length scales—constitute the kinetically preferred morphological spectrometry (DEMS) set-up equipped with an electrochemical end point of our Cu catalysts in flow conditions;50 a hypothesis capillarycell12withmilli-secondtimeresolutionenabledtracking that will be corroborated further below in our electrolyzer flow kinetic product formation rates and yields under transient catacell studies below. lyticCO2RR.Thankstoitstimeresolution,theDEMStechnique accurately captured the electrode potentials where product generation sets in (so-called onset potentials).</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5376,19 +9298,47 @@
           <t>S0442</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr">
+      <c r="D143" t="n">
+        <v>9</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Our CuO NS meet and ticles exposing stepped (310) facets are predicted be optimal exceed today’s top performing Cu catalysts under neutral nanocatalysts to support the EtOH-selective pathway. condition in electrolyzers.</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
         <is>
           <t>Methods Discussion Synthesis.NanosizedCuOcatalystwithsheet-likemorphologywassynthesizedby We have studied the synthesis and CO electrocatalysis of a asurfactant-freewet-chemistryroute.Nopurificationwasperformedforchemicals 2 (001)-orientedCuOnanosheetcatalyst.Evaluatedinelectrolyzers beforeuse.CuOnanosheetswereobtainedbythermaldecompositionofpresynthesizedCu(OH) intermediate.ToprepareCu(OH) intermediate,100mgCu under industrially relevant pH neutral conditions, the CuO NS 2 2 (SO) wasdissolvedin4mLDI-water,2.5mL1MKOHsolutionwasthenadded catalysts featured unprecedented performance metrics for C H 42 2 4 dropwiseintothesolution.After15-minstirring,1mLammoniumhydroxidewas and C 2+.</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr"/>
-      <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>In situ and ex situ TEM studies revealed that over added.Theresultinghomogeneouslightbluesolutionwasthentransferredtoa 10–20min under potential control the CuO NS fractured and— glasspressurevessel.Thesealedvesselwasthenheatedfromroomtemperatureto presumably limited by diffusion of Cu species—aggregated into 80°Cin30minandstayedat80°Cfor12hbeforeitwascooledtoroomtembranched,dendriticCustructuresthatrepresentedthefinalstable p 12 er ,6 a 4 tu 9 r .6 e 3 .T g h a e n p d ro fu d r u th ct e s r w p e u r r e ifi p e r d ec t i w pi i t c a e te b d y b e y th e a th n a o n l o a l n , d se w pa a r t a er te . d A v ft i e a r c w e a n r t d ri s fu th g e a y tio w n er a e t catalyst morphology under flow conditions.</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5410,27 +9360,55 @@
           <t>S0443</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr">
+      <c r="D144" t="n">
+        <v>2</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Therefore, the design of catalysts that selectively proFig.1e–gandiandSupplementaryFig.5.TheCu2p XPSfitting 3/2 duceethanol viaelectrochemical CO RRwere supposed tofocus curves revealed that Cu was mainly +1 and +2 valence in Cu/ 2 onminimizingthreecompetingreactionpathwayswhichreduced N C26,27.</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
         <is>
           <t>The Cu L3M45M45 Auger electron spectroscopy 0.14 thefaradaic efficiency(FE)ofasymmetricethanol byconsuming (AES) showed no distinct peak around 918.5eV which indicated electronsandprotons,thehydrogenevolutionreaction(HER),C thatnoCu0 existed onthesurface.TheN K-edgepresentedfour 1 product formation (e.g., CH , HCOOH) and other symmetrical obvious resonances (Fig. 1i) assigned peak A , A , and A to 4 1 2 3 C product formation (e.g., ethylene).</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr">
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>However, little is known pyridine-like, cyanide-like, and graphite-like N, respectively, 2 about the structure-activity relationship, extraordinarily to whereas A at ∼407eV is attributed to the transition from N 1s 4 explain the catalyst structure changes with the product changes corestatestoN−Cσ*bonds28.Obviously,peakA ofCu/N C 3 0.14 under different potential.</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr">
+      <c r="L144" t="inlineStr">
         <is>
           <t>P5:HCOO</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>uncertain</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr">
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5452,27 +9430,55 @@
           <t>S0444</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr">
+      <c r="D145" t="n">
+        <v>7</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Two with operando XAS and XPS results.</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
         <is>
           <t>On the other hand, the oxygen atoms may be from the adsorbed groups, such as OH*, infrared bands for CH 3 * over the Cu/C catalyst were not OCHO*(or CO ), as shown in Supplementary Fig. 19a, c.</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr">
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>The observed even after applying potential at −1.2V vs.</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="F145" t="inlineStr">
+      <c r="L145" t="inlineStr">
         <is>
           <t>P5:OCHO</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>uncertain</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5494,19 +9500,47 @@
           <t>S0445</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr">
+      <c r="D146" t="n">
+        <v>1</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>ARTICLE OPEN https://doi.org/10.1038/s41467-022-31427-9 – – Boosting electrocatalytic CO to ethanol 2 – production via asymmetric C C coupling Pengtang Wang1,2,4, Hao Yang 3,4, Cheng Tang1, Yu Wu3, Yao Zheng 1, Tao Cheng 3, Kenneth Davey 1, ✉ ✉ Xiaoqing Huang 2 &amp; Shi-Zhang Qiao 1 Electroreduction of carbon dioxide (CO ) into multicarbon products provides possibility of 2 large-scale chemicals production and is therefore of significant research and commercial interest.</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
         <is>
           <t>However, the production efficiency for ethanol (EtOH), a significant chemical feedstock, is impractically low because of limited selectivity, especially under high current operation.Herewereportanewsilver–modifiedcopper–oxidecatalyst(dCu O/Ag )that 2 2.3% exhibitsasignificantFaradaicefficiencyof40.8%andenergyefficiencyof22.3%forboosted EtOH production.</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr"/>
-      <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Importantly, it achieves CO –to–ethanol conversion under high current 2 operation with partial current density of 326.4mAcm−2 at −0.87V vs reversible hydrogen electrodeto rankhighlysignificantlyamongstreported Cu–basedcatalysts.</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5528,19 +9562,47 @@
           <t>S0446</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr">
+      <c r="D147" t="n">
+        <v>7</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>This bicarbonate species *OCO(OH) is formed as the dominant intermediate in the hydrogenation process of *CO catalyzed by 2 O2Sn = O.</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
         <is>
           <t>As a result of forming the strongly bound carbonate species, it hardly generates CO directly except from the recovered catalyst via 3 − 1 intermediate (as shown in Extended data Fig. 55b).</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr"/>
-      <c r="F147" t="inlineStr"/>
       <c r="G147" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>The differential charge distribution analysis and Bader charges of 3 determined that the positive charge was higher on the Sn atom, such that bonding between Sn atom and HCOOH (externally added or in-situ produced over SnS ) was favored.</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5562,19 +9624,47 @@
           <t>S0447</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr">
+      <c r="D148" t="n">
+        <v>2</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>We noted that the stable Cu–Ag phase boundaries, which may be a potential cause productionofacetateintheMEAelectrolyzerishigherthanthatinthe leadingtohigheractivityandselectivitytowardsC liquidproducts three-compartmentflowcell.Inaddition,asmallamountofpropio2+ comparedwiththosereportedCuAgbimetalliccatalystspreparedvia natewasalsodetectedafterCOelectrolysis(SupplementaryFig.5). other methods, such as galvanic replacement29,32,33, coThiscanbeattributedto(1)thereactionenvironmentontheanion electrodeposition34,andhigh-temperatureshock22. exchange membrane surface favors acetate formation and (2) the liquidproductsinMEAconfigurationarecollectedatanodeside(see Results “Methods”fordetails),whereaportionoftheproducedethanoland CORRperformanceoftheAg-modifiedCucatalysts n-propanolcanbeoxidizedtoacetateandpropionate,respectively.</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
         <is>
           <t>TheAg-modifiedCucatalystswerepreparedbyhigh-energyballmilTheseresultsareconsistentwiththepreviousliterature8,37,38. ling CuO particles with Ag powders with different atomic ratios of By normalizing the partial current densities of CORR with the Cu:Ag (0.9:0.1, 0.8:0.2, 0.7:0.3, 0.5:0.5) (see “Methods” for details). electrochemicallyactivesurfacearea(ECSA)forallcatalysts(SuppleCuO,insteadofmetallicCu,ischosenastheprecursorforballmilling mentaryFig.6andSupplementaryTables2and3),wefoundthatthe toavoidcoldweldingthatcanseverelyincreasethesizeandreducethe specific activity of C liquid product formations was improved in 2+ homogeneityofthesynthesizedmaterials35,36.Theas-preparedcataCu(OD) 1−x Ag x (x=0.1,0.2,0.3,0.5)comparedtoCu(OD),withoptimal lystsweresupportedontothemicroporouslayerofcarbonfiberpaper activity achieved in Cu(OD) Ag , while their specific activities of 0.8 0.2 asgas-diffusiontypeelectrodesforreactivityevaluationsin1MKOHin ethyleneformationweresimilar(SupplementaryFig.7a,b).C pro2+ a three-compartment microfluidic cell.</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr"/>
-      <c r="F148" t="inlineStr"/>
       <c r="G148" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Prior to reactivity measureducts are generally believed to form via a common and early ratements at different potentials, electrodes were pretreated with an determining step (RDS), either the coupling of two adsorbed CO insituelectroreductionataconstantcurrentdensityof−5mAcm−2for molecules39,40 orthe hydrogenationof CO41,the enhanced total C 2+ 5minstoconvertCuOintometallicCu(i.e.,oxide-derivedCu).The productformationratesindicatethattheadditionofAgaccelerates resultingcatalystsaredenotedasCu(OD) 1−x Ag x (x=0,0.1,0.2,0.3,0.5) thecommonRDS.Thecontrastingselectivity/ratetrendsofethylene inwhichCu(OD)standsforoxide-derivedCu. and C liquid products suggest that the introduction of Ag likely 2+ NatureCommunications|( 2023)1 4:698 2</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5596,19 +9686,43 @@
           <t>S0448</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr">
+      <c r="D149" t="n">
+        <v>2</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>TheAg-modifiedCucatalystswerepreparedbyhigh-energyballmilTheseresultsareconsistentwiththepreviousliterature8,37,38. ling CuO particles with Ag powders with different atomic ratios of By normalizing the partial current densities of CORR with the Cu:Ag (0.9:0.1, 0.8:0.2, 0.7:0.3, 0.5:0.5) (see “Methods” for details). electrochemicallyactivesurfacearea(ECSA)forallcatalysts(SuppleCuO,insteadofmetallicCu,ischosenastheprecursorforballmilling mentaryFig.6andSupplementaryTables2and3),wefoundthatthe toavoidcoldweldingthatcanseverelyincreasethesizeandreducethe specific activity of C liquid product formations was improved in 2+ homogeneityofthesynthesizedmaterials35,36.Theas-preparedcataCu(OD) 1−x Ag x (x=0.1,0.2,0.3,0.5)comparedtoCu(OD),withoptimal lystsweresupportedontothemicroporouslayerofcarbonfiberpaper activity achieved in Cu(OD) Ag , while their specific activities of 0.8 0.2 asgas-diffusiontypeelectrodesforreactivityevaluationsin1MKOHin ethyleneformationweresimilar(SupplementaryFig.7a,b).C pro2+ a three-compartment microfluidic cell.</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
         <is>
           <t>Prior to reactivity measureducts are generally believed to form via a common and early ratements at different potentials, electrodes were pretreated with an determining step (RDS), either the coupling of two adsorbed CO insituelectroreductionataconstantcurrentdensityof−5mAcm−2for molecules39,40 orthe hydrogenationof CO41,the enhanced total C 2+ 5minstoconvertCuOintometallicCu(i.e.,oxide-derivedCu).The productformationratesindicatethattheadditionofAgaccelerates resultingcatalystsaredenotedasCu(OD) 1−x Ag x (x=0,0.1,0.2,0.3,0.5) thecommonRDS.Thecontrastingselectivity/ratetrendsofethylene inwhichCu(OD)standsforoxide-derivedCu. and C liquid products suggest that the introduction of Ag likely 2+ NatureCommunications|( 2023)1 4:698 2</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr"/>
-      <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>uncertain</t>
-        </is>
-      </c>
+      <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5630,19 +9744,47 @@
           <t>S0449</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr">
+      <c r="D150" t="n">
+        <v>4</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Moreover, *CO coverage is determined by the local performance of Cu catalysts with different wettability for various concentration of CO near the catalyst.</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
         <is>
           <t>Thus, the coverage of key electrolyteswascompared(Fig.4a,b).TheHERperformanceshould intermediate*COcanbeimprovedbydirectlyusingCOasreactant. notbeaffectedbytheexternalgasdiffusionbutisdeterminedbyH O 2 WhentheCucatalysthasasimilarcontactangle,thepromotionof availability and transport26.</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr"/>
-      <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Therefore, stronger hydrophilicity can ethanol production is more obvious than that of ethylene during benefittheHERduetomoreefficientH Otransport. 2 CORR.</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5664,27 +9806,51 @@
           <t>S0450</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr">
+      <c r="D151" t="n">
+        <v>7</v>
+      </c>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr">
         <is>
           <t>2.5 2.0 1.5 1.0 0.5 0.0 CA: 131° CA: 156° thechangesof*COand*Hcoverage.Ingeneral,awider*COadsorption whereθisthecoverageoffreesurfacesites,E istheCO adsorption COx x voltageindicatesahigher*COcoverageinin-situATR-SEIRASspectra, energyonthesurface,RistheidealgasconstantandTisthetemwhile a larger decay distance of fluorescence intensity via CLSM perature.</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr">
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>The coverage of intermediate (θ ) is a function of CO COx representsalower*Hcoverage.Theexperimentaldatarevealthatthe adsorptionenergy(E )andlocalCO concentration([CO]).Tovary COx x x increaseofhydrophobicitywillleadtoanincreasing*COcoverageand theintermediate(*CO/*H)coverage,changingthelocalconcentration adecreasing*Hcoverage(Fig.5b). ofreactant(CO)atthecatalystlayerratherthan*CO/*Hadsorption x Further,thereactionpathwaysoncatalystsurfaceswithdifferent energyis,therefore,apromisingapproach.Comparedwiththeclaswettability can be understood (Fig. 5c).</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F151" t="inlineStr">
+      <c r="L151" t="inlineStr">
         <is>
           <t>P1:*COCO; P1:COCO</t>
         </is>
       </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>uncertain</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr">
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
         <is>
           <t>no</t>
         </is>
